--- a/光伏配储项目/电价数据/2026/坡头站.xlsx
+++ b/光伏配储项目/电价数据/2026/坡头站.xlsx
@@ -16,10 +16,9 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <numFmts count="3">
+  <numFmts count="2">
     <numFmt numFmtId="164" formatCode="yyyy-mm-dd h:mm:ss"/>
     <numFmt numFmtId="165" formatCode="YYYY-MM-DD HH:MM:SS"/>
-    <numFmt numFmtId="166" formatCode="yyyy/mm/dd"/>
   </numFmts>
   <fonts count="2">
     <font>
@@ -64,7 +63,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="1" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="166" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
@@ -430,13 +429,13 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CS116"/>
+  <dimension ref="A1:CS143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>日期</t>
+          <t>date</t>
         </is>
       </c>
       <c r="B1" s="1" t="inlineStr">
@@ -34613,6 +34612,7917 @@
       </c>
       <c r="CS116" t="n">
         <v>0.50989</v>
+      </c>
+    </row>
+    <row r="117">
+      <c r="A117" s="2" t="n">
+        <v>46138</v>
+      </c>
+      <c r="B117" t="n">
+        <v>0.38351</v>
+      </c>
+      <c r="C117" t="n">
+        <v>0.72088</v>
+      </c>
+      <c r="D117" t="n">
+        <v>0.56468</v>
+      </c>
+      <c r="E117" t="n">
+        <v>0.51638</v>
+      </c>
+      <c r="F117" t="n">
+        <v>0.45355</v>
+      </c>
+      <c r="G117" t="n">
+        <v>0.4482</v>
+      </c>
+      <c r="H117" t="n">
+        <v>0.43786</v>
+      </c>
+      <c r="I117" t="n">
+        <v>0.45468</v>
+      </c>
+      <c r="J117" t="n">
+        <v>0.43943</v>
+      </c>
+      <c r="K117" t="n">
+        <v>0.42325</v>
+      </c>
+      <c r="L117" t="n">
+        <v>0.41947</v>
+      </c>
+      <c r="M117" t="n">
+        <v>0.40892</v>
+      </c>
+      <c r="N117" t="n">
+        <v>0.39847</v>
+      </c>
+      <c r="O117" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="P117" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="Q117" t="n">
+        <v>0.40216</v>
+      </c>
+      <c r="R117" t="n">
+        <v>0.4234</v>
+      </c>
+      <c r="S117" t="n">
+        <v>0.41288</v>
+      </c>
+      <c r="T117" t="n">
+        <v>0.3549</v>
+      </c>
+      <c r="U117" t="n">
+        <v>0.39182</v>
+      </c>
+      <c r="V117" t="n">
+        <v>0.38511</v>
+      </c>
+      <c r="W117" t="n">
+        <v>0.41728</v>
+      </c>
+      <c r="X117" t="n">
+        <v>0.39204</v>
+      </c>
+      <c r="Y117" t="n">
+        <v>0.42075</v>
+      </c>
+      <c r="Z117" t="n">
+        <v>0.41425</v>
+      </c>
+      <c r="AA117" t="n">
+        <v>0.42423</v>
+      </c>
+      <c r="AB117" t="n">
+        <v>0.41306</v>
+      </c>
+      <c r="AC117" t="n">
+        <v>0.44425</v>
+      </c>
+      <c r="AD117" t="n">
+        <v>0.35765</v>
+      </c>
+      <c r="AE117" t="n">
+        <v>0.2999</v>
+      </c>
+      <c r="AF117" t="n">
+        <v>0.33548</v>
+      </c>
+      <c r="AG117" t="n">
+        <v>0.30828</v>
+      </c>
+      <c r="AH117" t="n">
+        <v>0.26793</v>
+      </c>
+      <c r="AI117" t="n">
+        <v>0.29488</v>
+      </c>
+      <c r="AJ117" t="n">
+        <v>0.30008</v>
+      </c>
+      <c r="AK117" t="n">
+        <v>0.21442</v>
+      </c>
+      <c r="AL117" t="n">
+        <v>0.2585</v>
+      </c>
+      <c r="AM117" t="n">
+        <v>0.07698000000000001</v>
+      </c>
+      <c r="AN117" t="n">
+        <v>0.06319</v>
+      </c>
+      <c r="AO117" t="n">
+        <v>0.05143</v>
+      </c>
+      <c r="AP117" t="n">
+        <v>0.032</v>
+      </c>
+      <c r="AQ117" t="n">
+        <v>0.05318</v>
+      </c>
+      <c r="AR117" t="n">
+        <v>0.03897999999999999</v>
+      </c>
+      <c r="AS117" t="n">
+        <v>0.04467</v>
+      </c>
+      <c r="AT117" t="n">
+        <v>0.008150000000000001</v>
+      </c>
+      <c r="AU117" t="n">
+        <v>-0.01774</v>
+      </c>
+      <c r="AV117" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW117" t="n">
+        <v>0.08620999999999999</v>
+      </c>
+      <c r="AX117" t="n">
+        <v>0.01521</v>
+      </c>
+      <c r="AY117" t="n">
+        <v>-0.00152</v>
+      </c>
+      <c r="AZ117" t="n">
+        <v>0.00355</v>
+      </c>
+      <c r="BA117" t="n">
+        <v>0.14523</v>
+      </c>
+      <c r="BB117" t="n">
+        <v>0.21298</v>
+      </c>
+      <c r="BC117" t="n">
+        <v>0.23616</v>
+      </c>
+      <c r="BD117" t="n">
+        <v>0.21368</v>
+      </c>
+      <c r="BE117" t="n">
+        <v>0.11525</v>
+      </c>
+      <c r="BF117" t="n">
+        <v>-0.0047</v>
+      </c>
+      <c r="BG117" t="n">
+        <v>-0.00693</v>
+      </c>
+      <c r="BH117" t="n">
+        <v>0.15538</v>
+      </c>
+      <c r="BI117" t="n">
+        <v>-0.01082</v>
+      </c>
+      <c r="BJ117" t="n">
+        <v>0.1908</v>
+      </c>
+      <c r="BK117" t="n">
+        <v>0.22316</v>
+      </c>
+      <c r="BL117" t="n">
+        <v>-0.01636</v>
+      </c>
+      <c r="BM117" t="n">
+        <v>-0.02612</v>
+      </c>
+      <c r="BN117" t="n">
+        <v>0.12257</v>
+      </c>
+      <c r="BO117" t="n">
+        <v>0.194</v>
+      </c>
+      <c r="BP117" t="n">
+        <v>0.26383</v>
+      </c>
+      <c r="BQ117" t="n">
+        <v>-0.008400000000000001</v>
+      </c>
+      <c r="BR117" t="n">
+        <v>0.2339</v>
+      </c>
+      <c r="BS117" t="n">
+        <v>-0.009769999999999999</v>
+      </c>
+      <c r="BT117" t="n">
+        <v>0.35697</v>
+      </c>
+      <c r="BU117" t="n">
+        <v>0.45399</v>
+      </c>
+      <c r="BV117" t="n">
+        <v>0.36652</v>
+      </c>
+      <c r="BW117" t="n">
+        <v>0.29514</v>
+      </c>
+      <c r="BX117" t="n">
+        <v>0.3552</v>
+      </c>
+      <c r="BY117" t="n">
+        <v>0.52758</v>
+      </c>
+      <c r="BZ117" t="n">
+        <v>0.34825</v>
+      </c>
+      <c r="CA117" t="n">
+        <v>0.4839</v>
+      </c>
+      <c r="CB117" t="n">
+        <v>0.7635299999999999</v>
+      </c>
+      <c r="CC117" t="n">
+        <v>0.61511</v>
+      </c>
+      <c r="CD117" t="n">
+        <v>0.51218</v>
+      </c>
+      <c r="CE117" t="n">
+        <v>0.51152</v>
+      </c>
+      <c r="CF117" t="n">
+        <v>0.13682</v>
+      </c>
+      <c r="CG117" t="n">
+        <v>0.38238</v>
+      </c>
+      <c r="CH117" t="n">
+        <v>0.5881000000000001</v>
+      </c>
+      <c r="CI117" t="n">
+        <v>0.5425800000000001</v>
+      </c>
+      <c r="CJ117" t="n">
+        <v>0.26931</v>
+      </c>
+      <c r="CK117" t="n">
+        <v>0.50099</v>
+      </c>
+      <c r="CL117" t="n">
+        <v>0.50399</v>
+      </c>
+      <c r="CM117" t="n">
+        <v>0.61581</v>
+      </c>
+      <c r="CN117" t="n">
+        <v>0.57211</v>
+      </c>
+      <c r="CO117" t="n">
+        <v>0.43372</v>
+      </c>
+      <c r="CP117" t="n">
+        <v>0.41854</v>
+      </c>
+      <c r="CQ117" t="n">
+        <v>0.40164</v>
+      </c>
+      <c r="CR117" t="n">
+        <v>0.31623</v>
+      </c>
+      <c r="CS117" t="n">
+        <v>0.3146</v>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="2" t="n">
+        <v>46139</v>
+      </c>
+      <c r="B118" t="n">
+        <v>0.33088</v>
+      </c>
+      <c r="C118" t="n">
+        <v>0.62414</v>
+      </c>
+      <c r="D118" t="n">
+        <v>1.43043</v>
+      </c>
+      <c r="E118" t="n">
+        <v>0.7569199999999999</v>
+      </c>
+      <c r="F118" t="n">
+        <v>1.33195</v>
+      </c>
+      <c r="G118" t="n">
+        <v>0.96651</v>
+      </c>
+      <c r="H118" t="n">
+        <v>0.5458200000000001</v>
+      </c>
+      <c r="I118" t="n">
+        <v>0.52765</v>
+      </c>
+      <c r="J118" t="n">
+        <v>0.5076700000000001</v>
+      </c>
+      <c r="K118" t="n">
+        <v>0.51573</v>
+      </c>
+      <c r="L118" t="n">
+        <v>0.51134</v>
+      </c>
+      <c r="M118" t="n">
+        <v>0.39504</v>
+      </c>
+      <c r="N118" t="n">
+        <v>0.47731</v>
+      </c>
+      <c r="O118" t="n">
+        <v>0.37451</v>
+      </c>
+      <c r="P118" t="n">
+        <v>0.38204</v>
+      </c>
+      <c r="Q118" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="R118" t="n">
+        <v>0.33861</v>
+      </c>
+      <c r="S118" t="n">
+        <v>0.37242</v>
+      </c>
+      <c r="T118" t="n">
+        <v>0.35784</v>
+      </c>
+      <c r="U118" t="n">
+        <v>0.36105</v>
+      </c>
+      <c r="V118" t="n">
+        <v>0.37736</v>
+      </c>
+      <c r="W118" t="n">
+        <v>0.37729</v>
+      </c>
+      <c r="X118" t="n">
+        <v>0.36124</v>
+      </c>
+      <c r="Y118" t="n">
+        <v>0.38224</v>
+      </c>
+      <c r="Z118" t="n">
+        <v>0.42539</v>
+      </c>
+      <c r="AA118" t="n">
+        <v>0.52834</v>
+      </c>
+      <c r="AB118" t="n">
+        <v>0.6549400000000001</v>
+      </c>
+      <c r="AC118" t="n">
+        <v>0.7523</v>
+      </c>
+      <c r="AD118" t="n">
+        <v>0.4428</v>
+      </c>
+      <c r="AE118" t="n">
+        <v>0.35556</v>
+      </c>
+      <c r="AF118" t="n">
+        <v>0.38941</v>
+      </c>
+      <c r="AG118" t="n">
+        <v>0.3083</v>
+      </c>
+      <c r="AH118" t="n">
+        <v>0.10202</v>
+      </c>
+      <c r="AI118" t="n">
+        <v>0.28638</v>
+      </c>
+      <c r="AJ118" t="n">
+        <v>0.44817</v>
+      </c>
+      <c r="AK118" t="n">
+        <v>0.089</v>
+      </c>
+      <c r="AL118" t="n">
+        <v>0.28869</v>
+      </c>
+      <c r="AM118" t="n">
+        <v>0.30248</v>
+      </c>
+      <c r="AN118" t="n">
+        <v>-0.04555</v>
+      </c>
+      <c r="AO118" t="n">
+        <v>0.26354</v>
+      </c>
+      <c r="AP118" t="n">
+        <v>0.18451</v>
+      </c>
+      <c r="AQ118" t="n">
+        <v>0.08242000000000001</v>
+      </c>
+      <c r="AR118" t="n">
+        <v>0.26822</v>
+      </c>
+      <c r="AS118" t="n">
+        <v>0.30457</v>
+      </c>
+      <c r="AT118" t="n">
+        <v>0.25764</v>
+      </c>
+      <c r="AU118" t="n">
+        <v>0.35825</v>
+      </c>
+      <c r="AV118" t="n">
+        <v>0.59073</v>
+      </c>
+      <c r="AW118" t="n">
+        <v>0.21631</v>
+      </c>
+      <c r="AX118" t="n">
+        <v>0.27572</v>
+      </c>
+      <c r="AY118" t="n">
+        <v>0.29343</v>
+      </c>
+      <c r="AZ118" t="n">
+        <v>0.32057</v>
+      </c>
+      <c r="BA118" t="n">
+        <v>0.32369</v>
+      </c>
+      <c r="BB118" t="n">
+        <v>0.27147</v>
+      </c>
+      <c r="BC118" t="n">
+        <v>0.5836399999999999</v>
+      </c>
+      <c r="BD118" t="n">
+        <v>0.39173</v>
+      </c>
+      <c r="BE118" t="n">
+        <v>0.33734</v>
+      </c>
+      <c r="BF118" t="n">
+        <v>-0.01807</v>
+      </c>
+      <c r="BG118" t="n">
+        <v>0.26707</v>
+      </c>
+      <c r="BH118" t="n">
+        <v>0.29885</v>
+      </c>
+      <c r="BI118" t="n">
+        <v>0.30684</v>
+      </c>
+      <c r="BJ118" t="n">
+        <v>0.26027</v>
+      </c>
+      <c r="BK118" t="n">
+        <v>0.30142</v>
+      </c>
+      <c r="BL118" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BM118" t="n">
+        <v>0.231</v>
+      </c>
+      <c r="BN118" t="n">
+        <v>0.15952</v>
+      </c>
+      <c r="BO118" t="n">
+        <v>0.23358</v>
+      </c>
+      <c r="BP118" t="n">
+        <v>0.25989</v>
+      </c>
+      <c r="BQ118" t="n">
+        <v>0.22298</v>
+      </c>
+      <c r="BR118" t="n">
+        <v>0.27262</v>
+      </c>
+      <c r="BS118" t="n">
+        <v>0.43904</v>
+      </c>
+      <c r="BT118" t="n">
+        <v>0.42351</v>
+      </c>
+      <c r="BU118" t="n">
+        <v>0.31522</v>
+      </c>
+      <c r="BV118" t="n">
+        <v>0.2681</v>
+      </c>
+      <c r="BW118" t="n">
+        <v>0.34986</v>
+      </c>
+      <c r="BX118" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="BY118" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="BZ118" t="n">
+        <v>0.28688</v>
+      </c>
+      <c r="CA118" t="n">
+        <v>0.70908</v>
+      </c>
+      <c r="CB118" t="n">
+        <v>1.03413</v>
+      </c>
+      <c r="CC118" t="n">
+        <v>0.93598</v>
+      </c>
+      <c r="CD118" t="n">
+        <v>0.27209</v>
+      </c>
+      <c r="CE118" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="CF118" t="n">
+        <v>0.84697</v>
+      </c>
+      <c r="CG118" t="n">
+        <v>0.4338</v>
+      </c>
+      <c r="CH118" t="n">
+        <v>0.38606</v>
+      </c>
+      <c r="CI118" t="n">
+        <v>0.8264900000000001</v>
+      </c>
+      <c r="CJ118" t="n">
+        <v>0.29165</v>
+      </c>
+      <c r="CK118" t="n">
+        <v>0.43829</v>
+      </c>
+      <c r="CL118" t="n">
+        <v>0.5986</v>
+      </c>
+      <c r="CM118" t="n">
+        <v>0.43915</v>
+      </c>
+      <c r="CN118" t="n">
+        <v>0.43383</v>
+      </c>
+      <c r="CO118" t="n">
+        <v>0.40788</v>
+      </c>
+      <c r="CP118" t="n">
+        <v>0.3334</v>
+      </c>
+      <c r="CQ118" t="n">
+        <v>0.33769</v>
+      </c>
+      <c r="CR118" t="n">
+        <v>0.29773</v>
+      </c>
+      <c r="CS118" t="n">
+        <v>0.31124</v>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="2" t="n">
+        <v>46140</v>
+      </c>
+      <c r="B119" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="C119" t="n">
+        <v>0.58296</v>
+      </c>
+      <c r="D119" t="n">
+        <v>0.36971</v>
+      </c>
+      <c r="E119" t="n">
+        <v>0.47399</v>
+      </c>
+      <c r="F119" t="n">
+        <v>0.36516</v>
+      </c>
+      <c r="G119" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="H119" t="n">
+        <v>0.40168</v>
+      </c>
+      <c r="I119" t="n">
+        <v>0.32354</v>
+      </c>
+      <c r="J119" t="n">
+        <v>0.3907</v>
+      </c>
+      <c r="K119" t="n">
+        <v>0.31717</v>
+      </c>
+      <c r="L119" t="n">
+        <v>0.29766</v>
+      </c>
+      <c r="M119" t="n">
+        <v>0.43287</v>
+      </c>
+      <c r="N119" t="n">
+        <v>0.44899</v>
+      </c>
+      <c r="O119" t="n">
+        <v>0.30986</v>
+      </c>
+      <c r="P119" t="n">
+        <v>0.37133</v>
+      </c>
+      <c r="Q119" t="n">
+        <v>0.3313</v>
+      </c>
+      <c r="R119" t="n">
+        <v>0.29727</v>
+      </c>
+      <c r="S119" t="n">
+        <v>0.37005</v>
+      </c>
+      <c r="T119" t="n">
+        <v>0.30226</v>
+      </c>
+      <c r="U119" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="V119" t="n">
+        <v>0.28956</v>
+      </c>
+      <c r="W119" t="n">
+        <v>0.29255</v>
+      </c>
+      <c r="X119" t="n">
+        <v>0.30206</v>
+      </c>
+      <c r="Y119" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="Z119" t="n">
+        <v>0.39646</v>
+      </c>
+      <c r="AA119" t="n">
+        <v>0.474</v>
+      </c>
+      <c r="AB119" t="n">
+        <v>0.44852</v>
+      </c>
+      <c r="AC119" t="n">
+        <v>0.44288</v>
+      </c>
+      <c r="AD119" t="n">
+        <v>0.36296</v>
+      </c>
+      <c r="AE119" t="n">
+        <v>0.42911</v>
+      </c>
+      <c r="AF119" t="n">
+        <v>0.36866</v>
+      </c>
+      <c r="AG119" t="n">
+        <v>0.39211</v>
+      </c>
+      <c r="AH119" t="n">
+        <v>0.40096</v>
+      </c>
+      <c r="AI119" t="n">
+        <v>0.32507</v>
+      </c>
+      <c r="AJ119" t="n">
+        <v>0.332</v>
+      </c>
+      <c r="AK119" t="n">
+        <v>0.28888</v>
+      </c>
+      <c r="AL119" t="n">
+        <v>0.50687</v>
+      </c>
+      <c r="AM119" t="n">
+        <v>0.23372</v>
+      </c>
+      <c r="AN119" t="n">
+        <v>0.52249</v>
+      </c>
+      <c r="AO119" t="n">
+        <v>0.03665</v>
+      </c>
+      <c r="AP119" t="n">
+        <v>0.56636</v>
+      </c>
+      <c r="AQ119" t="n">
+        <v>0.48614</v>
+      </c>
+      <c r="AR119" t="n">
+        <v>-0.01211</v>
+      </c>
+      <c r="AS119" t="n">
+        <v>0.38142</v>
+      </c>
+      <c r="AT119" t="n">
+        <v>0.46899</v>
+      </c>
+      <c r="AU119" t="n">
+        <v>0.44049</v>
+      </c>
+      <c r="AV119" t="n">
+        <v>0.44766</v>
+      </c>
+      <c r="AW119" t="n">
+        <v>0.5452100000000001</v>
+      </c>
+      <c r="AX119" t="n">
+        <v>-0.01513</v>
+      </c>
+      <c r="AY119" t="n">
+        <v>0.39737</v>
+      </c>
+      <c r="AZ119" t="n">
+        <v>0.26938</v>
+      </c>
+      <c r="BA119" t="n">
+        <v>0.28004</v>
+      </c>
+      <c r="BB119" t="n">
+        <v>0.07053</v>
+      </c>
+      <c r="BC119" t="n">
+        <v>0.21661</v>
+      </c>
+      <c r="BD119" t="n">
+        <v>0.14838</v>
+      </c>
+      <c r="BE119" t="n">
+        <v>0.20648</v>
+      </c>
+      <c r="BF119" t="n">
+        <v>0.19373</v>
+      </c>
+      <c r="BG119" t="n">
+        <v>0.24811</v>
+      </c>
+      <c r="BH119" t="n">
+        <v>0.29219</v>
+      </c>
+      <c r="BI119" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BJ119" t="n">
+        <v>0.29747</v>
+      </c>
+      <c r="BK119" t="n">
+        <v>0.27974</v>
+      </c>
+      <c r="BL119" t="n">
+        <v>0.29346</v>
+      </c>
+      <c r="BM119" t="n">
+        <v>0.32268</v>
+      </c>
+      <c r="BN119" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="BO119" t="n">
+        <v>0.34869</v>
+      </c>
+      <c r="BP119" t="n">
+        <v>0.28893</v>
+      </c>
+      <c r="BQ119" t="n">
+        <v>0.24825</v>
+      </c>
+      <c r="BR119" t="n">
+        <v>0.21659</v>
+      </c>
+      <c r="BS119" t="n">
+        <v>0.05239</v>
+      </c>
+      <c r="BT119" t="n">
+        <v>0.28282</v>
+      </c>
+      <c r="BU119" t="n">
+        <v>0.32281</v>
+      </c>
+      <c r="BV119" t="n">
+        <v>0.31703</v>
+      </c>
+      <c r="BW119" t="n">
+        <v>0.32311</v>
+      </c>
+      <c r="BX119" t="n">
+        <v>0.36034</v>
+      </c>
+      <c r="BY119" t="n">
+        <v>0.47902</v>
+      </c>
+      <c r="BZ119" t="n">
+        <v>-0.01386</v>
+      </c>
+      <c r="CA119" t="n">
+        <v>0.501</v>
+      </c>
+      <c r="CB119" t="n">
+        <v>0.3142799999999999</v>
+      </c>
+      <c r="CC119" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CD119" t="n">
+        <v>0.30423</v>
+      </c>
+      <c r="CE119" t="n">
+        <v>0.28965</v>
+      </c>
+      <c r="CF119" t="n">
+        <v>0.31949</v>
+      </c>
+      <c r="CG119" t="n">
+        <v>0.28892</v>
+      </c>
+      <c r="CH119" t="n">
+        <v>0.37385</v>
+      </c>
+      <c r="CI119" t="n">
+        <v>0.39475</v>
+      </c>
+      <c r="CJ119" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CK119" t="n">
+        <v>0.30173</v>
+      </c>
+      <c r="CL119" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="CM119" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="CN119" t="n">
+        <v>0.31745</v>
+      </c>
+      <c r="CO119" t="n">
+        <v>0.35433</v>
+      </c>
+      <c r="CP119" t="n">
+        <v>0.3523</v>
+      </c>
+      <c r="CQ119" t="n">
+        <v>0.34293</v>
+      </c>
+      <c r="CR119" t="n">
+        <v>0.35076</v>
+      </c>
+      <c r="CS119" t="n">
+        <v>0.3441</v>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="2" t="n">
+        <v>46141</v>
+      </c>
+      <c r="B120" t="n">
+        <v>0.32084</v>
+      </c>
+      <c r="C120" t="n">
+        <v>0.30009</v>
+      </c>
+      <c r="D120" t="n">
+        <v>0.34661</v>
+      </c>
+      <c r="E120" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="F120" t="n">
+        <v>0.31973</v>
+      </c>
+      <c r="G120" t="n">
+        <v>0.31292</v>
+      </c>
+      <c r="H120" t="n">
+        <v>0.3296</v>
+      </c>
+      <c r="I120" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="J120" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="K120" t="n">
+        <v>0.30154</v>
+      </c>
+      <c r="L120" t="n">
+        <v>0.27079</v>
+      </c>
+      <c r="M120" t="n">
+        <v>0.27427</v>
+      </c>
+      <c r="N120" t="n">
+        <v>0.47895</v>
+      </c>
+      <c r="O120" t="n">
+        <v>0.29148</v>
+      </c>
+      <c r="P120" t="n">
+        <v>0.30866</v>
+      </c>
+      <c r="Q120" t="n">
+        <v>0.27427</v>
+      </c>
+      <c r="R120" t="n">
+        <v>0.2988</v>
+      </c>
+      <c r="S120" t="n">
+        <v>0.30003</v>
+      </c>
+      <c r="T120" t="n">
+        <v>0.2815</v>
+      </c>
+      <c r="U120" t="n">
+        <v>0.28342</v>
+      </c>
+      <c r="V120" t="n">
+        <v>0.28013</v>
+      </c>
+      <c r="W120" t="n">
+        <v>0.28094</v>
+      </c>
+      <c r="X120" t="n">
+        <v>0.28076</v>
+      </c>
+      <c r="Y120" t="n">
+        <v>0.33936</v>
+      </c>
+      <c r="Z120" t="n">
+        <v>0.33923</v>
+      </c>
+      <c r="AA120" t="n">
+        <v>0.36437</v>
+      </c>
+      <c r="AB120" t="n">
+        <v>0.32276</v>
+      </c>
+      <c r="AC120" t="n">
+        <v>0.39061</v>
+      </c>
+      <c r="AD120" t="n">
+        <v>0.30052</v>
+      </c>
+      <c r="AE120" t="n">
+        <v>0.30696</v>
+      </c>
+      <c r="AF120" t="n">
+        <v>0.29887</v>
+      </c>
+      <c r="AG120" t="n">
+        <v>0.29687</v>
+      </c>
+      <c r="AH120" t="n">
+        <v>0.31254</v>
+      </c>
+      <c r="AI120" t="n">
+        <v>0.27943</v>
+      </c>
+      <c r="AJ120" t="n">
+        <v>0.26193</v>
+      </c>
+      <c r="AK120" t="n">
+        <v>0.26394</v>
+      </c>
+      <c r="AL120" t="n">
+        <v>0.19406</v>
+      </c>
+      <c r="AM120" t="n">
+        <v>0.10819</v>
+      </c>
+      <c r="AN120" t="n">
+        <v>0.11192</v>
+      </c>
+      <c r="AO120" t="n">
+        <v>0.08154</v>
+      </c>
+      <c r="AP120" t="n">
+        <v>0.25042</v>
+      </c>
+      <c r="AQ120" t="n">
+        <v>0.21223</v>
+      </c>
+      <c r="AR120" t="n">
+        <v>0.1314</v>
+      </c>
+      <c r="AS120" t="n">
+        <v>0.28844</v>
+      </c>
+      <c r="AT120" t="n">
+        <v>0.44875</v>
+      </c>
+      <c r="AU120" t="n">
+        <v>0.28932</v>
+      </c>
+      <c r="AV120" t="n">
+        <v>0.37602</v>
+      </c>
+      <c r="AW120" t="n">
+        <v>0.21364</v>
+      </c>
+      <c r="AX120" t="n">
+        <v>-0.04414</v>
+      </c>
+      <c r="AY120" t="n">
+        <v>-0.04508</v>
+      </c>
+      <c r="AZ120" t="n">
+        <v>0.06117</v>
+      </c>
+      <c r="BA120" t="n">
+        <v>0.27017</v>
+      </c>
+      <c r="BB120" t="n">
+        <v>0.17604</v>
+      </c>
+      <c r="BC120" t="n">
+        <v>0.04182</v>
+      </c>
+      <c r="BD120" t="n">
+        <v>-0.009050000000000001</v>
+      </c>
+      <c r="BE120" t="n">
+        <v>0.21293</v>
+      </c>
+      <c r="BF120" t="n">
+        <v>-0.00079</v>
+      </c>
+      <c r="BG120" t="n">
+        <v>0.03121</v>
+      </c>
+      <c r="BH120" t="n">
+        <v>0.04842</v>
+      </c>
+      <c r="BI120" t="n">
+        <v>0.07715999999999999</v>
+      </c>
+      <c r="BJ120" t="n">
+        <v>0.32655</v>
+      </c>
+      <c r="BK120" t="n">
+        <v>0.29329</v>
+      </c>
+      <c r="BL120" t="n">
+        <v>0.202</v>
+      </c>
+      <c r="BM120" t="n">
+        <v>0.16634</v>
+      </c>
+      <c r="BN120" t="n">
+        <v>0.20333</v>
+      </c>
+      <c r="BO120" t="n">
+        <v>0.1516</v>
+      </c>
+      <c r="BP120" t="n">
+        <v>0.19587</v>
+      </c>
+      <c r="BQ120" t="n">
+        <v>0.14228</v>
+      </c>
+      <c r="BR120" t="n">
+        <v>0.19996</v>
+      </c>
+      <c r="BS120" t="n">
+        <v>0.22738</v>
+      </c>
+      <c r="BT120" t="n">
+        <v>0.27917</v>
+      </c>
+      <c r="BU120" t="n">
+        <v>0.33467</v>
+      </c>
+      <c r="BV120" t="n">
+        <v>0.30875</v>
+      </c>
+      <c r="BW120" t="n">
+        <v>0.33699</v>
+      </c>
+      <c r="BX120" t="n">
+        <v>0.25762</v>
+      </c>
+      <c r="BY120" t="n">
+        <v>0.28709</v>
+      </c>
+      <c r="BZ120" t="n">
+        <v>0.30271</v>
+      </c>
+      <c r="CA120" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="CB120" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="CC120" t="n">
+        <v>0.38127</v>
+      </c>
+      <c r="CD120" t="n">
+        <v>0.36648</v>
+      </c>
+      <c r="CE120" t="n">
+        <v>0.30056</v>
+      </c>
+      <c r="CF120" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="CG120" t="n">
+        <v>0.30243</v>
+      </c>
+      <c r="CH120" t="n">
+        <v>0.3108399999999999</v>
+      </c>
+      <c r="CI120" t="n">
+        <v>0.29888</v>
+      </c>
+      <c r="CJ120" t="n">
+        <v>0.29695</v>
+      </c>
+      <c r="CK120" t="n">
+        <v>0.29303</v>
+      </c>
+      <c r="CL120" t="n">
+        <v>0.25555</v>
+      </c>
+      <c r="CM120" t="n">
+        <v>0.28858</v>
+      </c>
+      <c r="CN120" t="n">
+        <v>0.2837</v>
+      </c>
+      <c r="CO120" t="n">
+        <v>0.29434</v>
+      </c>
+      <c r="CP120" t="n">
+        <v>0.29221</v>
+      </c>
+      <c r="CQ120" t="n">
+        <v>0.29504</v>
+      </c>
+      <c r="CR120" t="n">
+        <v>0.28988</v>
+      </c>
+      <c r="CS120" t="n">
+        <v>0.29217</v>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="2" t="n">
+        <v>46142</v>
+      </c>
+      <c r="B121" t="n">
+        <v>0.3051</v>
+      </c>
+      <c r="C121" t="n">
+        <v>0.29771</v>
+      </c>
+      <c r="D121" t="n">
+        <v>0.34657</v>
+      </c>
+      <c r="E121" t="n">
+        <v>0.36718</v>
+      </c>
+      <c r="F121" t="n">
+        <v>0.3493</v>
+      </c>
+      <c r="G121" t="n">
+        <v>0.33288</v>
+      </c>
+      <c r="H121" t="n">
+        <v>0.3012</v>
+      </c>
+      <c r="I121" t="n">
+        <v>0.311</v>
+      </c>
+      <c r="J121" t="n">
+        <v>0.31103</v>
+      </c>
+      <c r="K121" t="n">
+        <v>0.30031</v>
+      </c>
+      <c r="L121" t="n">
+        <v>0.29833</v>
+      </c>
+      <c r="M121" t="n">
+        <v>0.27552</v>
+      </c>
+      <c r="N121" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="O121" t="n">
+        <v>0.2959</v>
+      </c>
+      <c r="P121" t="n">
+        <v>0.27386</v>
+      </c>
+      <c r="Q121" t="n">
+        <v>0.27662</v>
+      </c>
+      <c r="R121" t="n">
+        <v>0.29017</v>
+      </c>
+      <c r="S121" t="n">
+        <v>0.29016</v>
+      </c>
+      <c r="T121" t="n">
+        <v>0.29021</v>
+      </c>
+      <c r="U121" t="n">
+        <v>0.29802</v>
+      </c>
+      <c r="V121" t="n">
+        <v>0.29213</v>
+      </c>
+      <c r="W121" t="n">
+        <v>0.29513</v>
+      </c>
+      <c r="X121" t="n">
+        <v>0.31235</v>
+      </c>
+      <c r="Y121" t="n">
+        <v>0.30137</v>
+      </c>
+      <c r="Z121" t="n">
+        <v>0.31649</v>
+      </c>
+      <c r="AA121" t="n">
+        <v>0.32426</v>
+      </c>
+      <c r="AB121" t="n">
+        <v>0.32422</v>
+      </c>
+      <c r="AC121" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="AD121" t="n">
+        <v>0.32601</v>
+      </c>
+      <c r="AE121" t="n">
+        <v>0.2793</v>
+      </c>
+      <c r="AF121" t="n">
+        <v>0.26047</v>
+      </c>
+      <c r="AG121" t="n">
+        <v>0.04073</v>
+      </c>
+      <c r="AH121" t="n">
+        <v>0.04514</v>
+      </c>
+      <c r="AI121" t="n">
+        <v>0.04026</v>
+      </c>
+      <c r="AJ121" t="n">
+        <v>0.04001</v>
+      </c>
+      <c r="AK121" t="n">
+        <v>0.04268</v>
+      </c>
+      <c r="AL121" t="n">
+        <v>0.04503</v>
+      </c>
+      <c r="AM121" t="n">
+        <v>0.04352</v>
+      </c>
+      <c r="AN121" t="n">
+        <v>0.04554</v>
+      </c>
+      <c r="AO121" t="n">
+        <v>-0.0464</v>
+      </c>
+      <c r="AP121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ121" t="n">
+        <v>-0.04711</v>
+      </c>
+      <c r="AR121" t="n">
+        <v>-0.04792</v>
+      </c>
+      <c r="AS121" t="n">
+        <v>-0.04642</v>
+      </c>
+      <c r="AT121" t="n">
+        <v>-0.04675</v>
+      </c>
+      <c r="AU121" t="n">
+        <v>-0.0476</v>
+      </c>
+      <c r="AV121" t="n">
+        <v>-0.04681</v>
+      </c>
+      <c r="AW121" t="n">
+        <v>-0.04583</v>
+      </c>
+      <c r="AX121" t="n">
+        <v>-0.04797999999999999</v>
+      </c>
+      <c r="AY121" t="n">
+        <v>-0.0499</v>
+      </c>
+      <c r="AZ121" t="n">
+        <v>-0.04647</v>
+      </c>
+      <c r="BA121" t="n">
+        <v>-0.04795</v>
+      </c>
+      <c r="BB121" t="n">
+        <v>-0.04916</v>
+      </c>
+      <c r="BC121" t="n">
+        <v>-0.04876</v>
+      </c>
+      <c r="BD121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE121" t="n">
+        <v>-0.04645000000000001</v>
+      </c>
+      <c r="BF121" t="n">
+        <v>-0.04729999999999999</v>
+      </c>
+      <c r="BG121" t="n">
+        <v>0.22002</v>
+      </c>
+      <c r="BH121" t="n">
+        <v>0.04644</v>
+      </c>
+      <c r="BI121" t="n">
+        <v>0.04889</v>
+      </c>
+      <c r="BJ121" t="n">
+        <v>0.05167</v>
+      </c>
+      <c r="BK121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM121" t="n">
+        <v>-0.00213</v>
+      </c>
+      <c r="BN121" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO121" t="n">
+        <v>0.14709</v>
+      </c>
+      <c r="BP121" t="n">
+        <v>0.03758</v>
+      </c>
+      <c r="BQ121" t="n">
+        <v>0.09886</v>
+      </c>
+      <c r="BR121" t="n">
+        <v>0.28978</v>
+      </c>
+      <c r="BS121" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="BT121" t="n">
+        <v>0.2927</v>
+      </c>
+      <c r="BU121" t="n">
+        <v>0.31985</v>
+      </c>
+      <c r="BV121" t="n">
+        <v>0.32935</v>
+      </c>
+      <c r="BW121" t="n">
+        <v>0.3137200000000001</v>
+      </c>
+      <c r="BX121" t="n">
+        <v>0.3347</v>
+      </c>
+      <c r="BY121" t="n">
+        <v>0.32714</v>
+      </c>
+      <c r="BZ121" t="n">
+        <v>0.32872</v>
+      </c>
+      <c r="CA121" t="n">
+        <v>0.31733</v>
+      </c>
+      <c r="CB121" t="n">
+        <v>0.3673</v>
+      </c>
+      <c r="CC121" t="n">
+        <v>0.38551</v>
+      </c>
+      <c r="CD121" t="n">
+        <v>0.38008</v>
+      </c>
+      <c r="CE121" t="n">
+        <v>0.37762</v>
+      </c>
+      <c r="CF121" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="CG121" t="n">
+        <v>0.40062</v>
+      </c>
+      <c r="CH121" t="n">
+        <v>0.39545</v>
+      </c>
+      <c r="CI121" t="n">
+        <v>0.41227</v>
+      </c>
+      <c r="CJ121" t="n">
+        <v>0.46764</v>
+      </c>
+      <c r="CK121" t="n">
+        <v>0.35343</v>
+      </c>
+      <c r="CL121" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CM121" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="CN121" t="n">
+        <v>0.4173</v>
+      </c>
+      <c r="CO121" t="n">
+        <v>0.35505</v>
+      </c>
+      <c r="CP121" t="n">
+        <v>0.35811</v>
+      </c>
+      <c r="CQ121" t="n">
+        <v>0.34535</v>
+      </c>
+      <c r="CR121" t="n">
+        <v>0.35519</v>
+      </c>
+      <c r="CS121" t="n">
+        <v>0.35132</v>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="2" t="n">
+        <v>46143</v>
+      </c>
+      <c r="B122" t="n">
+        <v>0.36802</v>
+      </c>
+      <c r="C122" t="n">
+        <v>0.66442</v>
+      </c>
+      <c r="D122" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="E122" t="n">
+        <v>0.44655</v>
+      </c>
+      <c r="F122" t="n">
+        <v>0.42374</v>
+      </c>
+      <c r="G122" t="n">
+        <v>0.42381</v>
+      </c>
+      <c r="H122" t="n">
+        <v>0.35995</v>
+      </c>
+      <c r="I122" t="n">
+        <v>0.35949</v>
+      </c>
+      <c r="J122" t="n">
+        <v>0.35985</v>
+      </c>
+      <c r="K122" t="n">
+        <v>0.33536</v>
+      </c>
+      <c r="L122" t="n">
+        <v>0.31095</v>
+      </c>
+      <c r="M122" t="n">
+        <v>0.32631</v>
+      </c>
+      <c r="N122" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="O122" t="n">
+        <v>0.35715</v>
+      </c>
+      <c r="P122" t="n">
+        <v>0.34939</v>
+      </c>
+      <c r="Q122" t="n">
+        <v>0.34819</v>
+      </c>
+      <c r="R122" t="n">
+        <v>0.33507</v>
+      </c>
+      <c r="S122" t="n">
+        <v>0.31546</v>
+      </c>
+      <c r="T122" t="n">
+        <v>0.33027</v>
+      </c>
+      <c r="U122" t="n">
+        <v>0.33556</v>
+      </c>
+      <c r="V122" t="n">
+        <v>0.32274</v>
+      </c>
+      <c r="W122" t="n">
+        <v>0.30016</v>
+      </c>
+      <c r="X122" t="n">
+        <v>0.3228</v>
+      </c>
+      <c r="Y122" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="Z122" t="n">
+        <v>0.33907</v>
+      </c>
+      <c r="AA122" t="n">
+        <v>0.35027</v>
+      </c>
+      <c r="AB122" t="n">
+        <v>0.3521</v>
+      </c>
+      <c r="AC122" t="n">
+        <v>0.34288</v>
+      </c>
+      <c r="AD122" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AE122" t="n">
+        <v>0.10251</v>
+      </c>
+      <c r="AF122" t="n">
+        <v>0.10243</v>
+      </c>
+      <c r="AG122" t="n">
+        <v>0.04263</v>
+      </c>
+      <c r="AH122" t="n">
+        <v>-0.0459</v>
+      </c>
+      <c r="AI122" t="n">
+        <v>-0.04509000000000001</v>
+      </c>
+      <c r="AJ122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AK122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AL122" t="n">
+        <v>-0.04485</v>
+      </c>
+      <c r="AM122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="AN122" t="n">
+        <v>-0.04181</v>
+      </c>
+      <c r="AO122" t="n">
+        <v>-0.03235</v>
+      </c>
+      <c r="AP122" t="n">
+        <v>-0.04068</v>
+      </c>
+      <c r="AQ122" t="n">
+        <v>0.10694</v>
+      </c>
+      <c r="AR122" t="n">
+        <v>0.00108</v>
+      </c>
+      <c r="AS122" t="n">
+        <v>-0.03741</v>
+      </c>
+      <c r="AT122" t="n">
+        <v>-0.04688000000000001</v>
+      </c>
+      <c r="AU122" t="n">
+        <v>-0.04109</v>
+      </c>
+      <c r="AV122" t="n">
+        <v>-0.04126</v>
+      </c>
+      <c r="AW122" t="n">
+        <v>-0.04117</v>
+      </c>
+      <c r="AX122" t="n">
+        <v>-0.04374</v>
+      </c>
+      <c r="AY122" t="n">
+        <v>-0.04368</v>
+      </c>
+      <c r="AZ122" t="n">
+        <v>-0.04356</v>
+      </c>
+      <c r="BA122" t="n">
+        <v>-0.04106</v>
+      </c>
+      <c r="BB122" t="n">
+        <v>-0.04048</v>
+      </c>
+      <c r="BC122" t="n">
+        <v>-0.04327</v>
+      </c>
+      <c r="BD122" t="n">
+        <v>-0.04033</v>
+      </c>
+      <c r="BE122" t="n">
+        <v>-0.03896</v>
+      </c>
+      <c r="BF122" t="n">
+        <v>-0.044</v>
+      </c>
+      <c r="BG122" t="n">
+        <v>-0.04343</v>
+      </c>
+      <c r="BH122" t="n">
+        <v>-0.04372</v>
+      </c>
+      <c r="BI122" t="n">
+        <v>-0.04107</v>
+      </c>
+      <c r="BJ122" t="n">
+        <v>-0.04215</v>
+      </c>
+      <c r="BK122" t="n">
+        <v>-0.03997</v>
+      </c>
+      <c r="BL122" t="n">
+        <v>-0.04265</v>
+      </c>
+      <c r="BM122" t="n">
+        <v>-0.04992</v>
+      </c>
+      <c r="BN122" t="n">
+        <v>-0.04305</v>
+      </c>
+      <c r="BO122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BP122" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BQ122" t="n">
+        <v>-0.04643</v>
+      </c>
+      <c r="BR122" t="n">
+        <v>-0.04601</v>
+      </c>
+      <c r="BS122" t="n">
+        <v>0.20235</v>
+      </c>
+      <c r="BT122" t="n">
+        <v>0.14482</v>
+      </c>
+      <c r="BU122" t="n">
+        <v>0.29268</v>
+      </c>
+      <c r="BV122" t="n">
+        <v>0.2974</v>
+      </c>
+      <c r="BW122" t="n">
+        <v>0.30724</v>
+      </c>
+      <c r="BX122" t="n">
+        <v>0.3025</v>
+      </c>
+      <c r="BY122" t="n">
+        <v>0.29756</v>
+      </c>
+      <c r="BZ122" t="n">
+        <v>0.29484</v>
+      </c>
+      <c r="CA122" t="n">
+        <v>0.29634</v>
+      </c>
+      <c r="CB122" t="n">
+        <v>0.2954</v>
+      </c>
+      <c r="CC122" t="n">
+        <v>0.29972</v>
+      </c>
+      <c r="CD122" t="n">
+        <v>0.29341</v>
+      </c>
+      <c r="CE122" t="n">
+        <v>0.29735</v>
+      </c>
+      <c r="CF122" t="n">
+        <v>0.2714</v>
+      </c>
+      <c r="CG122" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="CH122" t="n">
+        <v>0.30049</v>
+      </c>
+      <c r="CI122" t="n">
+        <v>0.31018</v>
+      </c>
+      <c r="CJ122" t="n">
+        <v>0.30694</v>
+      </c>
+      <c r="CK122" t="n">
+        <v>0.30325</v>
+      </c>
+      <c r="CL122" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="CM122" t="n">
+        <v>0.32125</v>
+      </c>
+      <c r="CN122" t="n">
+        <v>0.35041</v>
+      </c>
+      <c r="CO122" t="n">
+        <v>0.35252</v>
+      </c>
+      <c r="CP122" t="n">
+        <v>0.34735</v>
+      </c>
+      <c r="CQ122" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="CR122" t="n">
+        <v>0.36787</v>
+      </c>
+      <c r="CS122" t="n">
+        <v>0.33776</v>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="2" t="n">
+        <v>46144</v>
+      </c>
+      <c r="B123" t="n">
+        <v>0.33293</v>
+      </c>
+      <c r="C123" t="n">
+        <v>1.32294</v>
+      </c>
+      <c r="D123" t="n">
+        <v>0.31335</v>
+      </c>
+      <c r="E123" t="n">
+        <v>0.40738</v>
+      </c>
+      <c r="F123" t="n">
+        <v>0.35256</v>
+      </c>
+      <c r="G123" t="n">
+        <v>0.32318</v>
+      </c>
+      <c r="H123" t="n">
+        <v>0.31129</v>
+      </c>
+      <c r="I123" t="n">
+        <v>0.3171</v>
+      </c>
+      <c r="J123" t="n">
+        <v>0.30394</v>
+      </c>
+      <c r="K123" t="n">
+        <v>0.28358</v>
+      </c>
+      <c r="L123" t="n">
+        <v>0.29787</v>
+      </c>
+      <c r="M123" t="n">
+        <v>0.29368</v>
+      </c>
+      <c r="N123" t="n">
+        <v>0.29056</v>
+      </c>
+      <c r="O123" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="P123" t="n">
+        <v>0.27353</v>
+      </c>
+      <c r="Q123" t="n">
+        <v>0.27368</v>
+      </c>
+      <c r="R123" t="n">
+        <v>0.2834</v>
+      </c>
+      <c r="S123" t="n">
+        <v>0.17437</v>
+      </c>
+      <c r="T123" t="n">
+        <v>0.16063</v>
+      </c>
+      <c r="U123" t="n">
+        <v>0.17326</v>
+      </c>
+      <c r="V123" t="n">
+        <v>0.1496</v>
+      </c>
+      <c r="W123" t="n">
+        <v>0.16132</v>
+      </c>
+      <c r="X123" t="n">
+        <v>0.1607</v>
+      </c>
+      <c r="Y123" t="n">
+        <v>0.23962</v>
+      </c>
+      <c r="Z123" t="n">
+        <v>0.21612</v>
+      </c>
+      <c r="AA123" t="n">
+        <v>0.22873</v>
+      </c>
+      <c r="AB123" t="n">
+        <v>0.27201</v>
+      </c>
+      <c r="AC123" t="n">
+        <v>0.28857</v>
+      </c>
+      <c r="AD123" t="n">
+        <v>0.29315</v>
+      </c>
+      <c r="AE123" t="n">
+        <v>0.32181</v>
+      </c>
+      <c r="AF123" t="n">
+        <v>0.29366</v>
+      </c>
+      <c r="AG123" t="n">
+        <v>0.28379</v>
+      </c>
+      <c r="AH123" t="n">
+        <v>0.28344</v>
+      </c>
+      <c r="AI123" t="n">
+        <v>0.28334</v>
+      </c>
+      <c r="AJ123" t="n">
+        <v>0.27087</v>
+      </c>
+      <c r="AK123" t="n">
+        <v>0.2832</v>
+      </c>
+      <c r="AL123" t="n">
+        <v>0.32546</v>
+      </c>
+      <c r="AM123" t="n">
+        <v>0.31318</v>
+      </c>
+      <c r="AN123" t="n">
+        <v>0.30783</v>
+      </c>
+      <c r="AO123" t="n">
+        <v>0.31725</v>
+      </c>
+      <c r="AP123" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="AQ123" t="n">
+        <v>0.36092</v>
+      </c>
+      <c r="AR123" t="n">
+        <v>0.27583</v>
+      </c>
+      <c r="AS123" t="n">
+        <v>-0.01379</v>
+      </c>
+      <c r="AT123" t="n">
+        <v>0.2779</v>
+      </c>
+      <c r="AU123" t="n">
+        <v>0.38208</v>
+      </c>
+      <c r="AV123" t="n">
+        <v>0.30557</v>
+      </c>
+      <c r="AW123" t="n">
+        <v>0.09615</v>
+      </c>
+      <c r="AX123" t="n">
+        <v>0.29139</v>
+      </c>
+      <c r="AY123" t="n">
+        <v>0.29637</v>
+      </c>
+      <c r="AZ123" t="n">
+        <v>0.29622</v>
+      </c>
+      <c r="BA123" t="n">
+        <v>0.39062</v>
+      </c>
+      <c r="BB123" t="n">
+        <v>0.31688</v>
+      </c>
+      <c r="BC123" t="n">
+        <v>0.29982</v>
+      </c>
+      <c r="BD123" t="n">
+        <v>0.30114</v>
+      </c>
+      <c r="BE123" t="n">
+        <v>0.29886</v>
+      </c>
+      <c r="BF123" t="n">
+        <v>0.3002</v>
+      </c>
+      <c r="BG123" t="n">
+        <v>0.15729</v>
+      </c>
+      <c r="BH123" t="n">
+        <v>0.19182</v>
+      </c>
+      <c r="BI123" t="n">
+        <v>0.28904</v>
+      </c>
+      <c r="BJ123" t="n">
+        <v>0.28907</v>
+      </c>
+      <c r="BK123" t="n">
+        <v>0.27346</v>
+      </c>
+      <c r="BL123" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="BM123" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="BN123" t="n">
+        <v>0.30059</v>
+      </c>
+      <c r="BO123" t="n">
+        <v>0.30804</v>
+      </c>
+      <c r="BP123" t="n">
+        <v>0.32356</v>
+      </c>
+      <c r="BQ123" t="n">
+        <v>0.47916</v>
+      </c>
+      <c r="BR123" t="n">
+        <v>0.5075</v>
+      </c>
+      <c r="BS123" t="n">
+        <v>0.79108</v>
+      </c>
+      <c r="BT123" t="n">
+        <v>0.6219199999999999</v>
+      </c>
+      <c r="BU123" t="n">
+        <v>0.78532</v>
+      </c>
+      <c r="BV123" t="n">
+        <v>0.39988</v>
+      </c>
+      <c r="BW123" t="n">
+        <v>0.49779</v>
+      </c>
+      <c r="BX123" t="n">
+        <v>0.78086</v>
+      </c>
+      <c r="BY123" t="n">
+        <v>0.92003</v>
+      </c>
+      <c r="BZ123" t="n">
+        <v>0.4943</v>
+      </c>
+      <c r="CA123" t="n">
+        <v>0.9280700000000001</v>
+      </c>
+      <c r="CB123" t="n">
+        <v>0.90689</v>
+      </c>
+      <c r="CC123" t="n">
+        <v>1.31949</v>
+      </c>
+      <c r="CD123" t="n">
+        <v>0.39653</v>
+      </c>
+      <c r="CE123" t="n">
+        <v>0.93002</v>
+      </c>
+      <c r="CF123" t="n">
+        <v>0.63881</v>
+      </c>
+      <c r="CG123" t="n">
+        <v>1.22887</v>
+      </c>
+      <c r="CH123" t="n">
+        <v>0.88948</v>
+      </c>
+      <c r="CI123" t="n">
+        <v>0.5807100000000001</v>
+      </c>
+      <c r="CJ123" t="n">
+        <v>1.37369</v>
+      </c>
+      <c r="CK123" t="n">
+        <v>1.06233</v>
+      </c>
+      <c r="CL123" t="n">
+        <v>0.57377</v>
+      </c>
+      <c r="CM123" t="n">
+        <v>0.8275</v>
+      </c>
+      <c r="CN123" t="n">
+        <v>0.53077</v>
+      </c>
+      <c r="CO123" t="n">
+        <v>0.80971</v>
+      </c>
+      <c r="CP123" t="n">
+        <v>0.80665</v>
+      </c>
+      <c r="CQ123" t="n">
+        <v>0.88129</v>
+      </c>
+      <c r="CR123" t="n">
+        <v>0.8930499999999999</v>
+      </c>
+      <c r="CS123" t="n">
+        <v>0.5274500000000001</v>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="2" t="n">
+        <v>46145</v>
+      </c>
+      <c r="B124" t="n">
+        <v>0.43217</v>
+      </c>
+      <c r="C124" t="n">
+        <v>1.44393</v>
+      </c>
+      <c r="D124" t="n">
+        <v>0.48909</v>
+      </c>
+      <c r="E124" t="n">
+        <v>1.25103</v>
+      </c>
+      <c r="F124" t="n">
+        <v>0.88007</v>
+      </c>
+      <c r="G124" t="n">
+        <v>0.55177</v>
+      </c>
+      <c r="H124" t="n">
+        <v>0.6655399999999999</v>
+      </c>
+      <c r="I124" t="n">
+        <v>0.5492</v>
+      </c>
+      <c r="J124" t="n">
+        <v>0.5102599999999999</v>
+      </c>
+      <c r="K124" t="n">
+        <v>0.46117</v>
+      </c>
+      <c r="L124" t="n">
+        <v>0.42942</v>
+      </c>
+      <c r="M124" t="n">
+        <v>0.44487</v>
+      </c>
+      <c r="N124" t="n">
+        <v>0.45203</v>
+      </c>
+      <c r="O124" t="n">
+        <v>0.39923</v>
+      </c>
+      <c r="P124" t="n">
+        <v>0.45326</v>
+      </c>
+      <c r="Q124" t="n">
+        <v>0.42238</v>
+      </c>
+      <c r="R124" t="n">
+        <v>0.35746</v>
+      </c>
+      <c r="S124" t="n">
+        <v>0.40047</v>
+      </c>
+      <c r="T124" t="n">
+        <v>0.36567</v>
+      </c>
+      <c r="U124" t="n">
+        <v>0.39681</v>
+      </c>
+      <c r="V124" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="W124" t="n">
+        <v>0.43438</v>
+      </c>
+      <c r="X124" t="n">
+        <v>0.34435</v>
+      </c>
+      <c r="Y124" t="n">
+        <v>0.39161</v>
+      </c>
+      <c r="Z124" t="n">
+        <v>0.35108</v>
+      </c>
+      <c r="AA124" t="n">
+        <v>0.3764</v>
+      </c>
+      <c r="AB124" t="n">
+        <v>0.37354</v>
+      </c>
+      <c r="AC124" t="n">
+        <v>0.36856</v>
+      </c>
+      <c r="AD124" t="n">
+        <v>0.41375</v>
+      </c>
+      <c r="AE124" t="n">
+        <v>0.36974</v>
+      </c>
+      <c r="AF124" t="n">
+        <v>0.45133</v>
+      </c>
+      <c r="AG124" t="n">
+        <v>0.35975</v>
+      </c>
+      <c r="AH124" t="n">
+        <v>0.40014</v>
+      </c>
+      <c r="AI124" t="n">
+        <v>0.40071</v>
+      </c>
+      <c r="AJ124" t="n">
+        <v>0.58969</v>
+      </c>
+      <c r="AK124" t="n">
+        <v>0.42855</v>
+      </c>
+      <c r="AL124" t="n">
+        <v>0.5968600000000001</v>
+      </c>
+      <c r="AM124" t="n">
+        <v>0.602</v>
+      </c>
+      <c r="AN124" t="n">
+        <v>0.64479</v>
+      </c>
+      <c r="AO124" t="n">
+        <v>0.45476</v>
+      </c>
+      <c r="AP124" t="n">
+        <v>0.3245</v>
+      </c>
+      <c r="AQ124" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="AR124" t="n">
+        <v>0.4474</v>
+      </c>
+      <c r="AS124" t="n">
+        <v>0.8650800000000001</v>
+      </c>
+      <c r="AT124" t="n">
+        <v>0.23938</v>
+      </c>
+      <c r="AU124" t="n">
+        <v>0.65483</v>
+      </c>
+      <c r="AV124" t="n">
+        <v>0.6389400000000001</v>
+      </c>
+      <c r="AW124" t="n">
+        <v>0.7751</v>
+      </c>
+      <c r="AX124" t="n">
+        <v>0.2367</v>
+      </c>
+      <c r="AY124" t="n">
+        <v>0.43425</v>
+      </c>
+      <c r="AZ124" t="n">
+        <v>0.31558</v>
+      </c>
+      <c r="BA124" t="n">
+        <v>0.32633</v>
+      </c>
+      <c r="BB124" t="n">
+        <v>0.30278</v>
+      </c>
+      <c r="BC124" t="n">
+        <v>-0.02321</v>
+      </c>
+      <c r="BD124" t="n">
+        <v>0.30025</v>
+      </c>
+      <c r="BE124" t="n">
+        <v>0.29416</v>
+      </c>
+      <c r="BF124" t="n">
+        <v>0.27332</v>
+      </c>
+      <c r="BG124" t="n">
+        <v>0.30333</v>
+      </c>
+      <c r="BH124" t="n">
+        <v>0.35943</v>
+      </c>
+      <c r="BI124" t="n">
+        <v>0.33258</v>
+      </c>
+      <c r="BJ124" t="n">
+        <v>0.31986</v>
+      </c>
+      <c r="BK124" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="BL124" t="n">
+        <v>0.34133</v>
+      </c>
+      <c r="BM124" t="n">
+        <v>0.31806</v>
+      </c>
+      <c r="BN124" t="n">
+        <v>0.30645</v>
+      </c>
+      <c r="BO124" t="n">
+        <v>0.31923</v>
+      </c>
+      <c r="BP124" t="n">
+        <v>0.3199</v>
+      </c>
+      <c r="BQ124" t="n">
+        <v>0.34426</v>
+      </c>
+      <c r="BR124" t="n">
+        <v>0.3148</v>
+      </c>
+      <c r="BS124" t="n">
+        <v>0.31492</v>
+      </c>
+      <c r="BT124" t="n">
+        <v>0.32061</v>
+      </c>
+      <c r="BU124" t="n">
+        <v>0.32321</v>
+      </c>
+      <c r="BV124" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="BW124" t="n">
+        <v>0.31273</v>
+      </c>
+      <c r="BX124" t="n">
+        <v>0.31411</v>
+      </c>
+      <c r="BY124" t="n">
+        <v>0.31287</v>
+      </c>
+      <c r="BZ124" t="n">
+        <v>0.31527</v>
+      </c>
+      <c r="CA124" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="CB124" t="n">
+        <v>0.31718</v>
+      </c>
+      <c r="CC124" t="n">
+        <v>0.32363</v>
+      </c>
+      <c r="CD124" t="n">
+        <v>0.32526</v>
+      </c>
+      <c r="CE124" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="CF124" t="n">
+        <v>0.35629</v>
+      </c>
+      <c r="CG124" t="n">
+        <v>0.34274</v>
+      </c>
+      <c r="CH124" t="n">
+        <v>0.34022</v>
+      </c>
+      <c r="CI124" t="n">
+        <v>0.33898</v>
+      </c>
+      <c r="CJ124" t="n">
+        <v>0.33083</v>
+      </c>
+      <c r="CK124" t="n">
+        <v>0.33751</v>
+      </c>
+      <c r="CL124" t="n">
+        <v>0.33561</v>
+      </c>
+      <c r="CM124" t="n">
+        <v>0.4103</v>
+      </c>
+      <c r="CN124" t="n">
+        <v>0.41299</v>
+      </c>
+      <c r="CO124" t="n">
+        <v>0.45282</v>
+      </c>
+      <c r="CP124" t="n">
+        <v>0.41535</v>
+      </c>
+      <c r="CQ124" t="n">
+        <v>0.3918</v>
+      </c>
+      <c r="CR124" t="n">
+        <v>0.37526</v>
+      </c>
+      <c r="CS124" t="n">
+        <v>0.35329</v>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="2" t="n">
+        <v>46146</v>
+      </c>
+      <c r="B125" t="n">
+        <v>0.33093</v>
+      </c>
+      <c r="C125" t="n">
+        <v>1.02542</v>
+      </c>
+      <c r="D125" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="E125" t="n">
+        <v>0.4996</v>
+      </c>
+      <c r="F125" t="n">
+        <v>0.502</v>
+      </c>
+      <c r="G125" t="n">
+        <v>0.62052</v>
+      </c>
+      <c r="H125" t="n">
+        <v>0.69496</v>
+      </c>
+      <c r="I125" t="n">
+        <v>0.41514</v>
+      </c>
+      <c r="J125" t="n">
+        <v>0.4099100000000001</v>
+      </c>
+      <c r="K125" t="n">
+        <v>0.45011</v>
+      </c>
+      <c r="L125" t="n">
+        <v>0.51163</v>
+      </c>
+      <c r="M125" t="n">
+        <v>0.44838</v>
+      </c>
+      <c r="N125" t="n">
+        <v>0.3655</v>
+      </c>
+      <c r="O125" t="n">
+        <v>0.38849</v>
+      </c>
+      <c r="P125" t="n">
+        <v>0.33091</v>
+      </c>
+      <c r="Q125" t="n">
+        <v>0.35956</v>
+      </c>
+      <c r="R125" t="n">
+        <v>0.3461</v>
+      </c>
+      <c r="S125" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="T125" t="n">
+        <v>0.40049</v>
+      </c>
+      <c r="U125" t="n">
+        <v>0.50063</v>
+      </c>
+      <c r="V125" t="n">
+        <v>0.35753</v>
+      </c>
+      <c r="W125" t="n">
+        <v>0.38796</v>
+      </c>
+      <c r="X125" t="n">
+        <v>0.34384</v>
+      </c>
+      <c r="Y125" t="n">
+        <v>0.35119</v>
+      </c>
+      <c r="Z125" t="n">
+        <v>0.35555</v>
+      </c>
+      <c r="AA125" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="AB125" t="n">
+        <v>0.35738</v>
+      </c>
+      <c r="AC125" t="n">
+        <v>0.36253</v>
+      </c>
+      <c r="AD125" t="n">
+        <v>0.31598</v>
+      </c>
+      <c r="AE125" t="n">
+        <v>0.31312</v>
+      </c>
+      <c r="AF125" t="n">
+        <v>0.33209</v>
+      </c>
+      <c r="AG125" t="n">
+        <v>0.33767</v>
+      </c>
+      <c r="AH125" t="n">
+        <v>0.33787</v>
+      </c>
+      <c r="AI125" t="n">
+        <v>0.34937</v>
+      </c>
+      <c r="AJ125" t="n">
+        <v>0.3153</v>
+      </c>
+      <c r="AK125" t="n">
+        <v>0.30429</v>
+      </c>
+      <c r="AL125" t="n">
+        <v>0.29062</v>
+      </c>
+      <c r="AM125" t="n">
+        <v>0.30393</v>
+      </c>
+      <c r="AN125" t="n">
+        <v>0.28912</v>
+      </c>
+      <c r="AO125" t="n">
+        <v>0.28071</v>
+      </c>
+      <c r="AP125" t="n">
+        <v>0.16474</v>
+      </c>
+      <c r="AQ125" t="n">
+        <v>0.28513</v>
+      </c>
+      <c r="AR125" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="AS125" t="n">
+        <v>0.32958</v>
+      </c>
+      <c r="AT125" t="n">
+        <v>0.30382</v>
+      </c>
+      <c r="AU125" t="n">
+        <v>0.314</v>
+      </c>
+      <c r="AV125" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AW125" t="n">
+        <v>0.26109</v>
+      </c>
+      <c r="AX125" t="n">
+        <v>0.20119</v>
+      </c>
+      <c r="AY125" t="n">
+        <v>0.27747</v>
+      </c>
+      <c r="AZ125" t="n">
+        <v>0.29212</v>
+      </c>
+      <c r="BA125" t="n">
+        <v>-0.01657</v>
+      </c>
+      <c r="BB125" t="n">
+        <v>0.27594</v>
+      </c>
+      <c r="BC125" t="n">
+        <v>0.29456</v>
+      </c>
+      <c r="BD125" t="n">
+        <v>0.27288</v>
+      </c>
+      <c r="BE125" t="n">
+        <v>0.25552</v>
+      </c>
+      <c r="BF125" t="n">
+        <v>0.30779</v>
+      </c>
+      <c r="BG125" t="n">
+        <v>0.28826</v>
+      </c>
+      <c r="BH125" t="n">
+        <v>0.29426</v>
+      </c>
+      <c r="BI125" t="n">
+        <v>0.31994</v>
+      </c>
+      <c r="BJ125" t="n">
+        <v>0.30518</v>
+      </c>
+      <c r="BK125" t="n">
+        <v>0.31299</v>
+      </c>
+      <c r="BL125" t="n">
+        <v>0.29048</v>
+      </c>
+      <c r="BM125" t="n">
+        <v>0.30388</v>
+      </c>
+      <c r="BN125" t="n">
+        <v>0.29102</v>
+      </c>
+      <c r="BO125" t="n">
+        <v>0.30904</v>
+      </c>
+      <c r="BP125" t="n">
+        <v>0.32043</v>
+      </c>
+      <c r="BQ125" t="n">
+        <v>0.31195</v>
+      </c>
+      <c r="BR125" t="n">
+        <v>0.2899</v>
+      </c>
+      <c r="BS125" t="n">
+        <v>0.34761</v>
+      </c>
+      <c r="BT125" t="n">
+        <v>0.25544</v>
+      </c>
+      <c r="BU125" t="n">
+        <v>0.35019</v>
+      </c>
+      <c r="BV125" t="n">
+        <v>0.32213</v>
+      </c>
+      <c r="BW125" t="n">
+        <v>0.24918</v>
+      </c>
+      <c r="BX125" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="BY125" t="n">
+        <v>0.27494</v>
+      </c>
+      <c r="BZ125" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="CA125" t="n">
+        <v>0.32888</v>
+      </c>
+      <c r="CB125" t="n">
+        <v>0.33881</v>
+      </c>
+      <c r="CC125" t="n">
+        <v>0.31006</v>
+      </c>
+      <c r="CD125" t="n">
+        <v>0.34952</v>
+      </c>
+      <c r="CE125" t="n">
+        <v>0.3102</v>
+      </c>
+      <c r="CF125" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="CG125" t="n">
+        <v>0.31776</v>
+      </c>
+      <c r="CH125" t="n">
+        <v>0.42817</v>
+      </c>
+      <c r="CI125" t="n">
+        <v>0.35005</v>
+      </c>
+      <c r="CJ125" t="n">
+        <v>0.24555</v>
+      </c>
+      <c r="CK125" t="n">
+        <v>0.42323</v>
+      </c>
+      <c r="CL125" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CM125" t="n">
+        <v>0.44701</v>
+      </c>
+      <c r="CN125" t="n">
+        <v>0.31163</v>
+      </c>
+      <c r="CO125" t="n">
+        <v>0.42072</v>
+      </c>
+      <c r="CP125" t="n">
+        <v>0.35907</v>
+      </c>
+      <c r="CQ125" t="n">
+        <v>0.40202</v>
+      </c>
+      <c r="CR125" t="n">
+        <v>0.40076</v>
+      </c>
+      <c r="CS125" t="n">
+        <v>0.59766</v>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="2" t="n">
+        <v>46147</v>
+      </c>
+      <c r="B126" t="n">
+        <v>0.35046</v>
+      </c>
+      <c r="C126" t="n">
+        <v>0.8897699999999999</v>
+      </c>
+      <c r="D126" t="n">
+        <v>1.35756</v>
+      </c>
+      <c r="E126" t="n">
+        <v>1.13655</v>
+      </c>
+      <c r="F126" t="n">
+        <v>0.7118300000000001</v>
+      </c>
+      <c r="G126" t="n">
+        <v>0.80586</v>
+      </c>
+      <c r="H126" t="n">
+        <v>0.65128</v>
+      </c>
+      <c r="I126" t="n">
+        <v>0.59093</v>
+      </c>
+      <c r="J126" t="n">
+        <v>0.45101</v>
+      </c>
+      <c r="K126" t="n">
+        <v>0.45033</v>
+      </c>
+      <c r="L126" t="n">
+        <v>0.50042</v>
+      </c>
+      <c r="M126" t="n">
+        <v>0.43989</v>
+      </c>
+      <c r="N126" t="n">
+        <v>0.43762</v>
+      </c>
+      <c r="O126" t="n">
+        <v>0.41505</v>
+      </c>
+      <c r="P126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="Q126" t="n">
+        <v>0.42367</v>
+      </c>
+      <c r="R126" t="n">
+        <v>0.5009</v>
+      </c>
+      <c r="S126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="T126" t="n">
+        <v>0.43406</v>
+      </c>
+      <c r="U126" t="n">
+        <v>0.41318</v>
+      </c>
+      <c r="V126" t="n">
+        <v>0.43409</v>
+      </c>
+      <c r="W126" t="n">
+        <v>0.39042</v>
+      </c>
+      <c r="X126" t="n">
+        <v>0.42832</v>
+      </c>
+      <c r="Y126" t="n">
+        <v>0.45075</v>
+      </c>
+      <c r="Z126" t="n">
+        <v>0.39632</v>
+      </c>
+      <c r="AA126" t="n">
+        <v>0.42348</v>
+      </c>
+      <c r="AB126" t="n">
+        <v>0.43442</v>
+      </c>
+      <c r="AC126" t="n">
+        <v>0.41292</v>
+      </c>
+      <c r="AD126" t="n">
+        <v>0.4129</v>
+      </c>
+      <c r="AE126" t="n">
+        <v>0.40051</v>
+      </c>
+      <c r="AF126" t="n">
+        <v>0.42385</v>
+      </c>
+      <c r="AG126" t="n">
+        <v>0.39604</v>
+      </c>
+      <c r="AH126" t="n">
+        <v>0.40269</v>
+      </c>
+      <c r="AI126" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AJ126" t="n">
+        <v>0.26644</v>
+      </c>
+      <c r="AK126" t="n">
+        <v>0.26632</v>
+      </c>
+      <c r="AL126" t="n">
+        <v>0.27176</v>
+      </c>
+      <c r="AM126" t="n">
+        <v>0.27933</v>
+      </c>
+      <c r="AN126" t="n">
+        <v>0.27055</v>
+      </c>
+      <c r="AO126" t="n">
+        <v>0.29643</v>
+      </c>
+      <c r="AP126" t="n">
+        <v>0.25685</v>
+      </c>
+      <c r="AQ126" t="n">
+        <v>0.2525</v>
+      </c>
+      <c r="AR126" t="n">
+        <v>0.24868</v>
+      </c>
+      <c r="AS126" t="n">
+        <v>0.25631</v>
+      </c>
+      <c r="AT126" t="n">
+        <v>-0.03071</v>
+      </c>
+      <c r="AU126" t="n">
+        <v>0.21185</v>
+      </c>
+      <c r="AV126" t="n">
+        <v>0.2678</v>
+      </c>
+      <c r="AW126" t="n">
+        <v>0.24645</v>
+      </c>
+      <c r="AX126" t="n">
+        <v>0.24997</v>
+      </c>
+      <c r="AY126" t="n">
+        <v>-0.008869999999999999</v>
+      </c>
+      <c r="AZ126" t="n">
+        <v>0.10625</v>
+      </c>
+      <c r="BA126" t="n">
+        <v>0.23815</v>
+      </c>
+      <c r="BB126" t="n">
+        <v>0.36504</v>
+      </c>
+      <c r="BC126" t="n">
+        <v>0.2852</v>
+      </c>
+      <c r="BD126" t="n">
+        <v>0.02371</v>
+      </c>
+      <c r="BE126" t="n">
+        <v>0.1465</v>
+      </c>
+      <c r="BF126" t="n">
+        <v>0.27768</v>
+      </c>
+      <c r="BG126" t="n">
+        <v>0.24522</v>
+      </c>
+      <c r="BH126" t="n">
+        <v>0.07087</v>
+      </c>
+      <c r="BI126" t="n">
+        <v>0.24617</v>
+      </c>
+      <c r="BJ126" t="n">
+        <v>0.26859</v>
+      </c>
+      <c r="BK126" t="n">
+        <v>0.30073</v>
+      </c>
+      <c r="BL126" t="n">
+        <v>0.24582</v>
+      </c>
+      <c r="BM126" t="n">
+        <v>0.30305</v>
+      </c>
+      <c r="BN126" t="n">
+        <v>0.27665</v>
+      </c>
+      <c r="BO126" t="n">
+        <v>0.29784</v>
+      </c>
+      <c r="BP126" t="n">
+        <v>0.29459</v>
+      </c>
+      <c r="BQ126" t="n">
+        <v>0.30758</v>
+      </c>
+      <c r="BR126" t="n">
+        <v>0.31456</v>
+      </c>
+      <c r="BS126" t="n">
+        <v>0.3401</v>
+      </c>
+      <c r="BT126" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="BU126" t="n">
+        <v>0.38871</v>
+      </c>
+      <c r="BV126" t="n">
+        <v>0.40004</v>
+      </c>
+      <c r="BW126" t="n">
+        <v>0.34749</v>
+      </c>
+      <c r="BX126" t="n">
+        <v>0.35941</v>
+      </c>
+      <c r="BY126" t="n">
+        <v>0.3397</v>
+      </c>
+      <c r="BZ126" t="n">
+        <v>0.33542</v>
+      </c>
+      <c r="CA126" t="n">
+        <v>0.38729</v>
+      </c>
+      <c r="CB126" t="n">
+        <v>0.48689</v>
+      </c>
+      <c r="CC126" t="n">
+        <v>0.3604</v>
+      </c>
+      <c r="CD126" t="n">
+        <v>0.43156</v>
+      </c>
+      <c r="CE126" t="n">
+        <v>0.36513</v>
+      </c>
+      <c r="CF126" t="n">
+        <v>0.35441</v>
+      </c>
+      <c r="CG126" t="n">
+        <v>0.60778</v>
+      </c>
+      <c r="CH126" t="n">
+        <v>0.46574</v>
+      </c>
+      <c r="CI126" t="n">
+        <v>0.6844199999999999</v>
+      </c>
+      <c r="CJ126" t="n">
+        <v>0.46673</v>
+      </c>
+      <c r="CK126" t="n">
+        <v>0.43961</v>
+      </c>
+      <c r="CL126" t="n">
+        <v>0.37688</v>
+      </c>
+      <c r="CM126" t="n">
+        <v>0.42562</v>
+      </c>
+      <c r="CN126" t="n">
+        <v>0.38818</v>
+      </c>
+      <c r="CO126" t="n">
+        <v>0.3713399999999999</v>
+      </c>
+      <c r="CP126" t="n">
+        <v>0.33636</v>
+      </c>
+      <c r="CQ126" t="n">
+        <v>0.3424</v>
+      </c>
+      <c r="CR126" t="n">
+        <v>0.3312</v>
+      </c>
+      <c r="CS126" t="n">
+        <v>0.32654</v>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="2" t="n">
+        <v>46148</v>
+      </c>
+      <c r="B127" t="n">
+        <v>0.32004</v>
+      </c>
+      <c r="C127" t="n">
+        <v>0.42574</v>
+      </c>
+      <c r="D127" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="E127" t="n">
+        <v>0.34626</v>
+      </c>
+      <c r="F127" t="n">
+        <v>0.3423</v>
+      </c>
+      <c r="G127" t="n">
+        <v>0.33791</v>
+      </c>
+      <c r="H127" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="I127" t="n">
+        <v>0.33162</v>
+      </c>
+      <c r="J127" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="K127" t="n">
+        <v>0.32709</v>
+      </c>
+      <c r="L127" t="n">
+        <v>0.3264</v>
+      </c>
+      <c r="M127" t="n">
+        <v>0.31209</v>
+      </c>
+      <c r="N127" t="n">
+        <v>0.32923</v>
+      </c>
+      <c r="O127" t="n">
+        <v>0.3282</v>
+      </c>
+      <c r="P127" t="n">
+        <v>0.32182</v>
+      </c>
+      <c r="Q127" t="n">
+        <v>0.31787</v>
+      </c>
+      <c r="R127" t="n">
+        <v>0.32205</v>
+      </c>
+      <c r="S127" t="n">
+        <v>0.32203</v>
+      </c>
+      <c r="T127" t="n">
+        <v>0.31169</v>
+      </c>
+      <c r="U127" t="n">
+        <v>0.32661</v>
+      </c>
+      <c r="V127" t="n">
+        <v>0.31267</v>
+      </c>
+      <c r="W127" t="n">
+        <v>0.32164</v>
+      </c>
+      <c r="X127" t="n">
+        <v>0.32232</v>
+      </c>
+      <c r="Y127" t="n">
+        <v>0.39373</v>
+      </c>
+      <c r="Z127" t="n">
+        <v>0.32761</v>
+      </c>
+      <c r="AA127" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="AB127" t="n">
+        <v>0.40226</v>
+      </c>
+      <c r="AC127" t="n">
+        <v>0.37699</v>
+      </c>
+      <c r="AD127" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="AE127" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="AF127" t="n">
+        <v>0.35669</v>
+      </c>
+      <c r="AG127" t="n">
+        <v>0.33368</v>
+      </c>
+      <c r="AH127" t="n">
+        <v>0.3126</v>
+      </c>
+      <c r="AI127" t="n">
+        <v>0.31099</v>
+      </c>
+      <c r="AJ127" t="n">
+        <v>0.0291</v>
+      </c>
+      <c r="AK127" t="n">
+        <v>0.30486</v>
+      </c>
+      <c r="AL127" t="n">
+        <v>0.29681</v>
+      </c>
+      <c r="AM127" t="n">
+        <v>0.03657</v>
+      </c>
+      <c r="AN127" t="n">
+        <v>0.2968</v>
+      </c>
+      <c r="AO127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AP127" t="n">
+        <v>0.29409</v>
+      </c>
+      <c r="AQ127" t="n">
+        <v>0.23721</v>
+      </c>
+      <c r="AR127" t="n">
+        <v>0.14652</v>
+      </c>
+      <c r="AS127" t="n">
+        <v>0.14921</v>
+      </c>
+      <c r="AT127" t="n">
+        <v>0.29534</v>
+      </c>
+      <c r="AU127" t="n">
+        <v>0.15616</v>
+      </c>
+      <c r="AV127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW127" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX127" t="n">
+        <v>0.1448</v>
+      </c>
+      <c r="AY127" t="n">
+        <v>0.14236</v>
+      </c>
+      <c r="AZ127" t="n">
+        <v>0.14485</v>
+      </c>
+      <c r="BA127" t="n">
+        <v>0.14377</v>
+      </c>
+      <c r="BB127" t="n">
+        <v>0.25897</v>
+      </c>
+      <c r="BC127" t="n">
+        <v>0.14548</v>
+      </c>
+      <c r="BD127" t="n">
+        <v>0.2687</v>
+      </c>
+      <c r="BE127" t="n">
+        <v>0.26882</v>
+      </c>
+      <c r="BF127" t="n">
+        <v>0.14336</v>
+      </c>
+      <c r="BG127" t="n">
+        <v>0.05313</v>
+      </c>
+      <c r="BH127" t="n">
+        <v>0.1148</v>
+      </c>
+      <c r="BI127" t="n">
+        <v>0.11373</v>
+      </c>
+      <c r="BJ127" t="n">
+        <v>0.1476</v>
+      </c>
+      <c r="BK127" t="n">
+        <v>0.14255</v>
+      </c>
+      <c r="BL127" t="n">
+        <v>0.1478</v>
+      </c>
+      <c r="BM127" t="n">
+        <v>0.28877</v>
+      </c>
+      <c r="BN127" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="BO127" t="n">
+        <v>0.30692</v>
+      </c>
+      <c r="BP127" t="n">
+        <v>0.28048</v>
+      </c>
+      <c r="BQ127" t="n">
+        <v>0.30269</v>
+      </c>
+      <c r="BR127" t="n">
+        <v>0.30963</v>
+      </c>
+      <c r="BS127" t="n">
+        <v>0.30647</v>
+      </c>
+      <c r="BT127" t="n">
+        <v>0.30969</v>
+      </c>
+      <c r="BU127" t="n">
+        <v>0.38271</v>
+      </c>
+      <c r="BV127" t="n">
+        <v>0.3445</v>
+      </c>
+      <c r="BW127" t="n">
+        <v>0.38115</v>
+      </c>
+      <c r="BX127" t="n">
+        <v>0.34669</v>
+      </c>
+      <c r="BY127" t="n">
+        <v>0.39867</v>
+      </c>
+      <c r="BZ127" t="n">
+        <v>0.36182</v>
+      </c>
+      <c r="CA127" t="n">
+        <v>0.38616</v>
+      </c>
+      <c r="CB127" t="n">
+        <v>0.45142</v>
+      </c>
+      <c r="CC127" t="n">
+        <v>0.40122</v>
+      </c>
+      <c r="CD127" t="n">
+        <v>0.39364</v>
+      </c>
+      <c r="CE127" t="n">
+        <v>0.40365</v>
+      </c>
+      <c r="CF127" t="n">
+        <v>0.39962</v>
+      </c>
+      <c r="CG127" t="n">
+        <v>0.43781</v>
+      </c>
+      <c r="CH127" t="n">
+        <v>0.44182</v>
+      </c>
+      <c r="CI127" t="n">
+        <v>0.44126</v>
+      </c>
+      <c r="CJ127" t="n">
+        <v>0.44621</v>
+      </c>
+      <c r="CK127" t="n">
+        <v>0.44547</v>
+      </c>
+      <c r="CL127" t="n">
+        <v>0.40427</v>
+      </c>
+      <c r="CM127" t="n">
+        <v>0.39188</v>
+      </c>
+      <c r="CN127" t="n">
+        <v>0.39905</v>
+      </c>
+      <c r="CO127" t="n">
+        <v>0.39276</v>
+      </c>
+      <c r="CP127" t="n">
+        <v>0.36118</v>
+      </c>
+      <c r="CQ127" t="n">
+        <v>0.36195</v>
+      </c>
+      <c r="CR127" t="n">
+        <v>0.3495</v>
+      </c>
+      <c r="CS127" t="n">
+        <v>0.3507</v>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="2" t="n">
+        <v>46149</v>
+      </c>
+      <c r="B128" t="n">
+        <v>0.34108</v>
+      </c>
+      <c r="C128" t="n">
+        <v>0.43715</v>
+      </c>
+      <c r="D128" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="E128" t="n">
+        <v>0.47036</v>
+      </c>
+      <c r="F128" t="n">
+        <v>0.42544</v>
+      </c>
+      <c r="G128" t="n">
+        <v>0.41745</v>
+      </c>
+      <c r="H128" t="n">
+        <v>0.37056</v>
+      </c>
+      <c r="I128" t="n">
+        <v>0.38261</v>
+      </c>
+      <c r="J128" t="n">
+        <v>0.38207</v>
+      </c>
+      <c r="K128" t="n">
+        <v>0.39465</v>
+      </c>
+      <c r="L128" t="n">
+        <v>0.38137</v>
+      </c>
+      <c r="M128" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="N128" t="n">
+        <v>0.38076</v>
+      </c>
+      <c r="O128" t="n">
+        <v>0.36052</v>
+      </c>
+      <c r="P128" t="n">
+        <v>0.39164</v>
+      </c>
+      <c r="Q128" t="n">
+        <v>0.37072</v>
+      </c>
+      <c r="R128" t="n">
+        <v>0.38081</v>
+      </c>
+      <c r="S128" t="n">
+        <v>0.35066</v>
+      </c>
+      <c r="T128" t="n">
+        <v>0.34767</v>
+      </c>
+      <c r="U128" t="n">
+        <v>0.35568</v>
+      </c>
+      <c r="V128" t="n">
+        <v>0.34528</v>
+      </c>
+      <c r="W128" t="n">
+        <v>0.34061</v>
+      </c>
+      <c r="X128" t="n">
+        <v>0.34562</v>
+      </c>
+      <c r="Y128" t="n">
+        <v>0.34062</v>
+      </c>
+      <c r="Z128" t="n">
+        <v>0.34522</v>
+      </c>
+      <c r="AA128" t="n">
+        <v>0.35588</v>
+      </c>
+      <c r="AB128" t="n">
+        <v>0.37067</v>
+      </c>
+      <c r="AC128" t="n">
+        <v>0.38036</v>
+      </c>
+      <c r="AD128" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="AE128" t="n">
+        <v>0.34016</v>
+      </c>
+      <c r="AF128" t="n">
+        <v>0.34048</v>
+      </c>
+      <c r="AG128" t="n">
+        <v>0.3404700000000001</v>
+      </c>
+      <c r="AH128" t="n">
+        <v>0.30612</v>
+      </c>
+      <c r="AI128" t="n">
+        <v>0.30953</v>
+      </c>
+      <c r="AJ128" t="n">
+        <v>0.29107</v>
+      </c>
+      <c r="AK128" t="n">
+        <v>-0.01527</v>
+      </c>
+      <c r="AL128" t="n">
+        <v>-0.00234</v>
+      </c>
+      <c r="AM128" t="n">
+        <v>0.25037</v>
+      </c>
+      <c r="AN128" t="n">
+        <v>0.25057</v>
+      </c>
+      <c r="AO128" t="n">
+        <v>0.24293</v>
+      </c>
+      <c r="AP128" t="n">
+        <v>-0.015</v>
+      </c>
+      <c r="AQ128" t="n">
+        <v>0.18411</v>
+      </c>
+      <c r="AR128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS128" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT128" t="n">
+        <v>0.09353</v>
+      </c>
+      <c r="AU128" t="n">
+        <v>-0.01685</v>
+      </c>
+      <c r="AV128" t="n">
+        <v>0.14882</v>
+      </c>
+      <c r="AW128" t="n">
+        <v>-0.01482</v>
+      </c>
+      <c r="AX128" t="n">
+        <v>-0.0154</v>
+      </c>
+      <c r="AY128" t="n">
+        <v>0.20094</v>
+      </c>
+      <c r="AZ128" t="n">
+        <v>0.17982</v>
+      </c>
+      <c r="BA128" t="n">
+        <v>0.30327</v>
+      </c>
+      <c r="BB128" t="n">
+        <v>-0.01053</v>
+      </c>
+      <c r="BC128" t="n">
+        <v>0.19864</v>
+      </c>
+      <c r="BD128" t="n">
+        <v>0.20891</v>
+      </c>
+      <c r="BE128" t="n">
+        <v>-0.01671</v>
+      </c>
+      <c r="BF128" t="n">
+        <v>0.19288</v>
+      </c>
+      <c r="BG128" t="n">
+        <v>0.18147</v>
+      </c>
+      <c r="BH128" t="n">
+        <v>-0.01426</v>
+      </c>
+      <c r="BI128" t="n">
+        <v>0.21344</v>
+      </c>
+      <c r="BJ128" t="n">
+        <v>-0.01594</v>
+      </c>
+      <c r="BK128" t="n">
+        <v>0.21046</v>
+      </c>
+      <c r="BL128" t="n">
+        <v>-0.01646</v>
+      </c>
+      <c r="BM128" t="n">
+        <v>0.008070000000000001</v>
+      </c>
+      <c r="BN128" t="n">
+        <v>0.29909</v>
+      </c>
+      <c r="BO128" t="n">
+        <v>0.28357</v>
+      </c>
+      <c r="BP128" t="n">
+        <v>0.28831</v>
+      </c>
+      <c r="BQ128" t="n">
+        <v>0.32406</v>
+      </c>
+      <c r="BR128" t="n">
+        <v>0.29814</v>
+      </c>
+      <c r="BS128" t="n">
+        <v>0.31125</v>
+      </c>
+      <c r="BT128" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="BU128" t="n">
+        <v>0.33228</v>
+      </c>
+      <c r="BV128" t="n">
+        <v>0.35021</v>
+      </c>
+      <c r="BW128" t="n">
+        <v>0.34942</v>
+      </c>
+      <c r="BX128" t="n">
+        <v>0.36993</v>
+      </c>
+      <c r="BY128" t="n">
+        <v>0.36848</v>
+      </c>
+      <c r="BZ128" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CA128" t="n">
+        <v>0.44654</v>
+      </c>
+      <c r="CB128" t="n">
+        <v>0.45943</v>
+      </c>
+      <c r="CC128" t="n">
+        <v>0.2494</v>
+      </c>
+      <c r="CD128" t="n">
+        <v>0.426</v>
+      </c>
+      <c r="CE128" t="n">
+        <v>0.38422</v>
+      </c>
+      <c r="CF128" t="n">
+        <v>0.35501</v>
+      </c>
+      <c r="CG128" t="n">
+        <v>0.3575</v>
+      </c>
+      <c r="CH128" t="n">
+        <v>0.35509</v>
+      </c>
+      <c r="CI128" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CJ128" t="n">
+        <v>0.5125299999999999</v>
+      </c>
+      <c r="CK128" t="n">
+        <v>0.34896</v>
+      </c>
+      <c r="CL128" t="n">
+        <v>0.36767</v>
+      </c>
+      <c r="CM128" t="n">
+        <v>0.37076</v>
+      </c>
+      <c r="CN128" t="n">
+        <v>0.36054</v>
+      </c>
+      <c r="CO128" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CP128" t="n">
+        <v>0.38039</v>
+      </c>
+      <c r="CQ128" t="n">
+        <v>0.38577</v>
+      </c>
+      <c r="CR128" t="n">
+        <v>0.35052</v>
+      </c>
+      <c r="CS128" t="n">
+        <v>0.36064</v>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="2" t="n">
+        <v>46150</v>
+      </c>
+      <c r="B129" t="n">
+        <v>0.34043</v>
+      </c>
+      <c r="C129" t="n">
+        <v>0.36663</v>
+      </c>
+      <c r="D129" t="n">
+        <v>0.42043</v>
+      </c>
+      <c r="E129" t="n">
+        <v>0.37094</v>
+      </c>
+      <c r="F129" t="n">
+        <v>0.39231</v>
+      </c>
+      <c r="G129" t="n">
+        <v>0.3812</v>
+      </c>
+      <c r="H129" t="n">
+        <v>0.35327</v>
+      </c>
+      <c r="I129" t="n">
+        <v>0.34991</v>
+      </c>
+      <c r="J129" t="n">
+        <v>0.3608</v>
+      </c>
+      <c r="K129" t="n">
+        <v>0.35212</v>
+      </c>
+      <c r="L129" t="n">
+        <v>0.34251</v>
+      </c>
+      <c r="M129" t="n">
+        <v>0.34814</v>
+      </c>
+      <c r="N129" t="n">
+        <v>0.34615</v>
+      </c>
+      <c r="O129" t="n">
+        <v>0.35013</v>
+      </c>
+      <c r="P129" t="n">
+        <v>0.34747</v>
+      </c>
+      <c r="Q129" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="R129" t="n">
+        <v>0.341</v>
+      </c>
+      <c r="S129" t="n">
+        <v>0.34254</v>
+      </c>
+      <c r="T129" t="n">
+        <v>0.34365</v>
+      </c>
+      <c r="U129" t="n">
+        <v>0.33892</v>
+      </c>
+      <c r="V129" t="n">
+        <v>0.3387</v>
+      </c>
+      <c r="W129" t="n">
+        <v>0.34054</v>
+      </c>
+      <c r="X129" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="Y129" t="n">
+        <v>0.34164</v>
+      </c>
+      <c r="Z129" t="n">
+        <v>0.33262</v>
+      </c>
+      <c r="AA129" t="n">
+        <v>0.35064</v>
+      </c>
+      <c r="AB129" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AC129" t="n">
+        <v>0.36194</v>
+      </c>
+      <c r="AD129" t="n">
+        <v>0.31305</v>
+      </c>
+      <c r="AE129" t="n">
+        <v>0.32949</v>
+      </c>
+      <c r="AF129" t="n">
+        <v>0.33958</v>
+      </c>
+      <c r="AG129" t="n">
+        <v>0.32596</v>
+      </c>
+      <c r="AH129" t="n">
+        <v>0.31882</v>
+      </c>
+      <c r="AI129" t="n">
+        <v>0.33199</v>
+      </c>
+      <c r="AJ129" t="n">
+        <v>0.32081</v>
+      </c>
+      <c r="AK129" t="n">
+        <v>0.31147</v>
+      </c>
+      <c r="AL129" t="n">
+        <v>0.35959</v>
+      </c>
+      <c r="AM129" t="n">
+        <v>0.30493</v>
+      </c>
+      <c r="AN129" t="n">
+        <v>0.28458</v>
+      </c>
+      <c r="AO129" t="n">
+        <v>0.26646</v>
+      </c>
+      <c r="AP129" t="n">
+        <v>0.32338</v>
+      </c>
+      <c r="AQ129" t="n">
+        <v>0.23931</v>
+      </c>
+      <c r="AR129" t="n">
+        <v>0.28395</v>
+      </c>
+      <c r="AS129" t="n">
+        <v>0.25204</v>
+      </c>
+      <c r="AT129" t="n">
+        <v>0.26987</v>
+      </c>
+      <c r="AU129" t="n">
+        <v>0.27976</v>
+      </c>
+      <c r="AV129" t="n">
+        <v>-0.03314</v>
+      </c>
+      <c r="AW129" t="n">
+        <v>0.25451</v>
+      </c>
+      <c r="AX129" t="n">
+        <v>0.24999</v>
+      </c>
+      <c r="AY129" t="n">
+        <v>0.21016</v>
+      </c>
+      <c r="AZ129" t="n">
+        <v>0.07501000000000001</v>
+      </c>
+      <c r="BA129" t="n">
+        <v>0.1844</v>
+      </c>
+      <c r="BB129" t="n">
+        <v>0.24497</v>
+      </c>
+      <c r="BC129" t="n">
+        <v>0.28639</v>
+      </c>
+      <c r="BD129" t="n">
+        <v>0.3105</v>
+      </c>
+      <c r="BE129" t="n">
+        <v>0.27112</v>
+      </c>
+      <c r="BF129" t="n">
+        <v>0.25317</v>
+      </c>
+      <c r="BG129" t="n">
+        <v>0.29796</v>
+      </c>
+      <c r="BH129" t="n">
+        <v>0.31253</v>
+      </c>
+      <c r="BI129" t="n">
+        <v>0.30537</v>
+      </c>
+      <c r="BJ129" t="n">
+        <v>0.27456</v>
+      </c>
+      <c r="BK129" t="n">
+        <v>0.29725</v>
+      </c>
+      <c r="BL129" t="n">
+        <v>0.33092</v>
+      </c>
+      <c r="BM129" t="n">
+        <v>0.32735</v>
+      </c>
+      <c r="BN129" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="BO129" t="n">
+        <v>0.42817</v>
+      </c>
+      <c r="BP129" t="n">
+        <v>0.34948</v>
+      </c>
+      <c r="BQ129" t="n">
+        <v>0.33731</v>
+      </c>
+      <c r="BR129" t="n">
+        <v>0.34866</v>
+      </c>
+      <c r="BS129" t="n">
+        <v>0.35789</v>
+      </c>
+      <c r="BT129" t="n">
+        <v>0.31642</v>
+      </c>
+      <c r="BU129" t="n">
+        <v>0.39309</v>
+      </c>
+      <c r="BV129" t="n">
+        <v>0.32343</v>
+      </c>
+      <c r="BW129" t="n">
+        <v>0.32865</v>
+      </c>
+      <c r="BX129" t="n">
+        <v>0.33396</v>
+      </c>
+      <c r="BY129" t="n">
+        <v>0.34339</v>
+      </c>
+      <c r="BZ129" t="n">
+        <v>0.33276</v>
+      </c>
+      <c r="CA129" t="n">
+        <v>0.50583</v>
+      </c>
+      <c r="CB129" t="n">
+        <v>0.41625</v>
+      </c>
+      <c r="CC129" t="n">
+        <v>0.77751</v>
+      </c>
+      <c r="CD129" t="n">
+        <v>0.36833</v>
+      </c>
+      <c r="CE129" t="n">
+        <v>0.45074</v>
+      </c>
+      <c r="CF129" t="n">
+        <v>0.33501</v>
+      </c>
+      <c r="CG129" t="n">
+        <v>0.33798</v>
+      </c>
+      <c r="CH129" t="n">
+        <v>0.35058</v>
+      </c>
+      <c r="CI129" t="n">
+        <v>0.4686</v>
+      </c>
+      <c r="CJ129" t="n">
+        <v>0.43591</v>
+      </c>
+      <c r="CK129" t="n">
+        <v>0.41727</v>
+      </c>
+      <c r="CL129" t="n">
+        <v>0.31064</v>
+      </c>
+      <c r="CM129" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="CN129" t="n">
+        <v>0.35606</v>
+      </c>
+      <c r="CO129" t="n">
+        <v>0.35855</v>
+      </c>
+      <c r="CP129" t="n">
+        <v>0.32684</v>
+      </c>
+      <c r="CQ129" t="n">
+        <v>0.31244</v>
+      </c>
+      <c r="CR129" t="n">
+        <v>0.32776</v>
+      </c>
+      <c r="CS129" t="n">
+        <v>0.31016</v>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="2" t="n">
+        <v>46151</v>
+      </c>
+      <c r="B130" t="n">
+        <v>0.34824</v>
+      </c>
+      <c r="C130" t="n">
+        <v>0.30496</v>
+      </c>
+      <c r="D130" t="n">
+        <v>0.34307</v>
+      </c>
+      <c r="E130" t="n">
+        <v>0.33153</v>
+      </c>
+      <c r="F130" t="n">
+        <v>0.32841</v>
+      </c>
+      <c r="G130" t="n">
+        <v>0.32535</v>
+      </c>
+      <c r="H130" t="n">
+        <v>0.33032</v>
+      </c>
+      <c r="I130" t="n">
+        <v>0.32525</v>
+      </c>
+      <c r="J130" t="n">
+        <v>0.3255</v>
+      </c>
+      <c r="K130" t="n">
+        <v>0.32881</v>
+      </c>
+      <c r="L130" t="n">
+        <v>0.32416</v>
+      </c>
+      <c r="M130" t="n">
+        <v>0.32689</v>
+      </c>
+      <c r="N130" t="n">
+        <v>0.32466</v>
+      </c>
+      <c r="O130" t="n">
+        <v>0.32754</v>
+      </c>
+      <c r="P130" t="n">
+        <v>0.32886</v>
+      </c>
+      <c r="Q130" t="n">
+        <v>0.32744</v>
+      </c>
+      <c r="R130" t="n">
+        <v>0.32778</v>
+      </c>
+      <c r="S130" t="n">
+        <v>0.32434</v>
+      </c>
+      <c r="T130" t="n">
+        <v>0.33136</v>
+      </c>
+      <c r="U130" t="n">
+        <v>0.32651</v>
+      </c>
+      <c r="V130" t="n">
+        <v>0.32127</v>
+      </c>
+      <c r="W130" t="n">
+        <v>0.31974</v>
+      </c>
+      <c r="X130" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="Y130" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="Z130" t="n">
+        <v>0.33112</v>
+      </c>
+      <c r="AA130" t="n">
+        <v>0.33541</v>
+      </c>
+      <c r="AB130" t="n">
+        <v>0.34667</v>
+      </c>
+      <c r="AC130" t="n">
+        <v>0.34121</v>
+      </c>
+      <c r="AD130" t="n">
+        <v>0.34129</v>
+      </c>
+      <c r="AE130" t="n">
+        <v>0.33586</v>
+      </c>
+      <c r="AF130" t="n">
+        <v>0.33917</v>
+      </c>
+      <c r="AG130" t="n">
+        <v>0.32167</v>
+      </c>
+      <c r="AH130" t="n">
+        <v>0.32148</v>
+      </c>
+      <c r="AI130" t="n">
+        <v>0.33454</v>
+      </c>
+      <c r="AJ130" t="n">
+        <v>0.34882</v>
+      </c>
+      <c r="AK130" t="n">
+        <v>0.35323</v>
+      </c>
+      <c r="AL130" t="n">
+        <v>0.32979</v>
+      </c>
+      <c r="AM130" t="n">
+        <v>0.32334</v>
+      </c>
+      <c r="AN130" t="n">
+        <v>0.31867</v>
+      </c>
+      <c r="AO130" t="n">
+        <v>0.31674</v>
+      </c>
+      <c r="AP130" t="n">
+        <v>0.32351</v>
+      </c>
+      <c r="AQ130" t="n">
+        <v>0.31421</v>
+      </c>
+      <c r="AR130" t="n">
+        <v>0.28765</v>
+      </c>
+      <c r="AS130" t="n">
+        <v>-0.01974</v>
+      </c>
+      <c r="AT130" t="n">
+        <v>0.29039</v>
+      </c>
+      <c r="AU130" t="n">
+        <v>0.29038</v>
+      </c>
+      <c r="AV130" t="n">
+        <v>-0.02043</v>
+      </c>
+      <c r="AW130" t="n">
+        <v>0.31432</v>
+      </c>
+      <c r="AX130" t="n">
+        <v>0.28263</v>
+      </c>
+      <c r="AY130" t="n">
+        <v>0.31451</v>
+      </c>
+      <c r="AZ130" t="n">
+        <v>0.31864</v>
+      </c>
+      <c r="BA130" t="n">
+        <v>0.29096</v>
+      </c>
+      <c r="BB130" t="n">
+        <v>0.32051</v>
+      </c>
+      <c r="BC130" t="n">
+        <v>0.32864</v>
+      </c>
+      <c r="BD130" t="n">
+        <v>0.31714</v>
+      </c>
+      <c r="BE130" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BF130" t="n">
+        <v>0.32075</v>
+      </c>
+      <c r="BG130" t="n">
+        <v>0.31764</v>
+      </c>
+      <c r="BH130" t="n">
+        <v>0.31494</v>
+      </c>
+      <c r="BI130" t="n">
+        <v>0.31996</v>
+      </c>
+      <c r="BJ130" t="n">
+        <v>0.31958</v>
+      </c>
+      <c r="BK130" t="n">
+        <v>0.31338</v>
+      </c>
+      <c r="BL130" t="n">
+        <v>0.3491</v>
+      </c>
+      <c r="BM130" t="n">
+        <v>0.30433</v>
+      </c>
+      <c r="BN130" t="n">
+        <v>0.28757</v>
+      </c>
+      <c r="BO130" t="n">
+        <v>0.31589</v>
+      </c>
+      <c r="BP130" t="n">
+        <v>0.3463</v>
+      </c>
+      <c r="BQ130" t="n">
+        <v>0.29151</v>
+      </c>
+      <c r="BR130" t="n">
+        <v>0.34125</v>
+      </c>
+      <c r="BS130" t="n">
+        <v>0.32295</v>
+      </c>
+      <c r="BT130" t="n">
+        <v>0.35011</v>
+      </c>
+      <c r="BU130" t="n">
+        <v>0.35014</v>
+      </c>
+      <c r="BV130" t="n">
+        <v>0.35015</v>
+      </c>
+      <c r="BW130" t="n">
+        <v>0.36014</v>
+      </c>
+      <c r="BX130" t="n">
+        <v>0.3272</v>
+      </c>
+      <c r="BY130" t="n">
+        <v>0.32959</v>
+      </c>
+      <c r="BZ130" t="n">
+        <v>0.34774</v>
+      </c>
+      <c r="CA130" t="n">
+        <v>0.37794</v>
+      </c>
+      <c r="CB130" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="CC130" t="n">
+        <v>0.36358</v>
+      </c>
+      <c r="CD130" t="n">
+        <v>0.36997</v>
+      </c>
+      <c r="CE130" t="n">
+        <v>0.36421</v>
+      </c>
+      <c r="CF130" t="n">
+        <v>0.37502</v>
+      </c>
+      <c r="CG130" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CH130" t="n">
+        <v>0.39611</v>
+      </c>
+      <c r="CI130" t="n">
+        <v>0.38562</v>
+      </c>
+      <c r="CJ130" t="n">
+        <v>0.37166</v>
+      </c>
+      <c r="CK130" t="n">
+        <v>0.40429</v>
+      </c>
+      <c r="CL130" t="n">
+        <v>0.35504</v>
+      </c>
+      <c r="CM130" t="n">
+        <v>0.38083</v>
+      </c>
+      <c r="CN130" t="n">
+        <v>0.37185</v>
+      </c>
+      <c r="CO130" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="CP130" t="n">
+        <v>0.35055</v>
+      </c>
+      <c r="CQ130" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="CR130" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="CS130" t="n">
+        <v>0.34228</v>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="2" t="n">
+        <v>46152</v>
+      </c>
+      <c r="B131" t="n">
+        <v>0.33995</v>
+      </c>
+      <c r="C131" t="n">
+        <v>0.35274</v>
+      </c>
+      <c r="D131" t="n">
+        <v>0.36223</v>
+      </c>
+      <c r="E131" t="n">
+        <v>0.36089</v>
+      </c>
+      <c r="F131" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="G131" t="n">
+        <v>0.35089</v>
+      </c>
+      <c r="H131" t="n">
+        <v>0.35009</v>
+      </c>
+      <c r="I131" t="n">
+        <v>0.34995</v>
+      </c>
+      <c r="J131" t="n">
+        <v>0.34984</v>
+      </c>
+      <c r="K131" t="n">
+        <v>0.34666</v>
+      </c>
+      <c r="L131" t="n">
+        <v>0.36091</v>
+      </c>
+      <c r="M131" t="n">
+        <v>0.34746</v>
+      </c>
+      <c r="N131" t="n">
+        <v>0.35071</v>
+      </c>
+      <c r="O131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="P131" t="n">
+        <v>0.33714</v>
+      </c>
+      <c r="Q131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="R131" t="n">
+        <v>0.3400899999999999</v>
+      </c>
+      <c r="S131" t="n">
+        <v>0.34</v>
+      </c>
+      <c r="T131" t="n">
+        <v>0.37006</v>
+      </c>
+      <c r="U131" t="n">
+        <v>0.32443</v>
+      </c>
+      <c r="V131" t="n">
+        <v>0.33869</v>
+      </c>
+      <c r="W131" t="n">
+        <v>0.33993</v>
+      </c>
+      <c r="X131" t="n">
+        <v>0.34998</v>
+      </c>
+      <c r="Y131" t="n">
+        <v>0.33702</v>
+      </c>
+      <c r="Z131" t="n">
+        <v>0.34004</v>
+      </c>
+      <c r="AA131" t="n">
+        <v>0.34509</v>
+      </c>
+      <c r="AB131" t="n">
+        <v>0.33624</v>
+      </c>
+      <c r="AC131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AD131" t="n">
+        <v>0.34997</v>
+      </c>
+      <c r="AE131" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="AF131" t="n">
+        <v>0.34019</v>
+      </c>
+      <c r="AG131" t="n">
+        <v>0.32815</v>
+      </c>
+      <c r="AH131" t="n">
+        <v>0.34901</v>
+      </c>
+      <c r="AI131" t="n">
+        <v>0.33996</v>
+      </c>
+      <c r="AJ131" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="AK131" t="n">
+        <v>0.33634</v>
+      </c>
+      <c r="AL131" t="n">
+        <v>-0.04051</v>
+      </c>
+      <c r="AM131" t="n">
+        <v>0.32635</v>
+      </c>
+      <c r="AN131" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="AO131" t="n">
+        <v>0.31877</v>
+      </c>
+      <c r="AP131" t="n">
+        <v>0.32538</v>
+      </c>
+      <c r="AQ131" t="n">
+        <v>0.3184</v>
+      </c>
+      <c r="AR131" t="n">
+        <v>0.31801</v>
+      </c>
+      <c r="AS131" t="n">
+        <v>0.31836</v>
+      </c>
+      <c r="AT131" t="n">
+        <v>0.31846</v>
+      </c>
+      <c r="AU131" t="n">
+        <v>0.31963</v>
+      </c>
+      <c r="AV131" t="n">
+        <v>0.31984</v>
+      </c>
+      <c r="AW131" t="n">
+        <v>0.31793</v>
+      </c>
+      <c r="AX131" t="n">
+        <v>0.31908</v>
+      </c>
+      <c r="AY131" t="n">
+        <v>0.37082</v>
+      </c>
+      <c r="AZ131" t="n">
+        <v>0.31049</v>
+      </c>
+      <c r="BA131" t="n">
+        <v>0.32047</v>
+      </c>
+      <c r="BB131" t="n">
+        <v>0.31826</v>
+      </c>
+      <c r="BC131" t="n">
+        <v>0.31584</v>
+      </c>
+      <c r="BD131" t="n">
+        <v>0.32394</v>
+      </c>
+      <c r="BE131" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BF131" t="n">
+        <v>0.31944</v>
+      </c>
+      <c r="BG131" t="n">
+        <v>0.3194</v>
+      </c>
+      <c r="BH131" t="n">
+        <v>0.32294</v>
+      </c>
+      <c r="BI131" t="n">
+        <v>0.32971</v>
+      </c>
+      <c r="BJ131" t="n">
+        <v>0.325</v>
+      </c>
+      <c r="BK131" t="n">
+        <v>0.32845</v>
+      </c>
+      <c r="BL131" t="n">
+        <v>0.32423</v>
+      </c>
+      <c r="BM131" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="BN131" t="n">
+        <v>0.349</v>
+      </c>
+      <c r="BO131" t="n">
+        <v>0.7360599999999999</v>
+      </c>
+      <c r="BP131" t="n">
+        <v>0.41599</v>
+      </c>
+      <c r="BQ131" t="n">
+        <v>0.35514</v>
+      </c>
+      <c r="BR131" t="n">
+        <v>0.35945</v>
+      </c>
+      <c r="BS131" t="n">
+        <v>0.36707</v>
+      </c>
+      <c r="BT131" t="n">
+        <v>0.35105</v>
+      </c>
+      <c r="BU131" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="BV131" t="n">
+        <v>0.34826</v>
+      </c>
+      <c r="BW131" t="n">
+        <v>0.36135</v>
+      </c>
+      <c r="BX131" t="n">
+        <v>0.36129</v>
+      </c>
+      <c r="BY131" t="n">
+        <v>0.36332</v>
+      </c>
+      <c r="BZ131" t="n">
+        <v>0.35127</v>
+      </c>
+      <c r="CA131" t="n">
+        <v>0.3786</v>
+      </c>
+      <c r="CB131" t="n">
+        <v>0.38126</v>
+      </c>
+      <c r="CC131" t="n">
+        <v>0.38215</v>
+      </c>
+      <c r="CD131" t="n">
+        <v>0.38267</v>
+      </c>
+      <c r="CE131" t="n">
+        <v>0.42955</v>
+      </c>
+      <c r="CF131" t="n">
+        <v>0.40733</v>
+      </c>
+      <c r="CG131" t="n">
+        <v>0.39056</v>
+      </c>
+      <c r="CH131" t="n">
+        <v>0.39172</v>
+      </c>
+      <c r="CI131" t="n">
+        <v>0.64955</v>
+      </c>
+      <c r="CJ131" t="n">
+        <v>0.87697</v>
+      </c>
+      <c r="CK131" t="n">
+        <v>0.48735</v>
+      </c>
+      <c r="CL131" t="n">
+        <v>0.48633</v>
+      </c>
+      <c r="CM131" t="n">
+        <v>0.46043</v>
+      </c>
+      <c r="CN131" t="n">
+        <v>0.39419</v>
+      </c>
+      <c r="CO131" t="n">
+        <v>0.351</v>
+      </c>
+      <c r="CP131" t="n">
+        <v>0.35104</v>
+      </c>
+      <c r="CQ131" t="n">
+        <v>0.35997</v>
+      </c>
+      <c r="CR131" t="n">
+        <v>0.34012</v>
+      </c>
+      <c r="CS131" t="n">
+        <v>0.34507</v>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="2" t="n">
+        <v>46154</v>
+      </c>
+      <c r="B132" t="n">
+        <v>0.32044</v>
+      </c>
+      <c r="C132" t="n">
+        <v>0.41166</v>
+      </c>
+      <c r="D132" t="n">
+        <v>0.37648</v>
+      </c>
+      <c r="E132" t="n">
+        <v>0.37188</v>
+      </c>
+      <c r="F132" t="n">
+        <v>0.36381</v>
+      </c>
+      <c r="G132" t="n">
+        <v>0.36018</v>
+      </c>
+      <c r="H132" t="n">
+        <v>0.36015</v>
+      </c>
+      <c r="I132" t="n">
+        <v>0.36319</v>
+      </c>
+      <c r="J132" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="K132" t="n">
+        <v>0.36123</v>
+      </c>
+      <c r="L132" t="n">
+        <v>0.36022</v>
+      </c>
+      <c r="M132" t="n">
+        <v>0.35418</v>
+      </c>
+      <c r="N132" t="n">
+        <v>0.36116</v>
+      </c>
+      <c r="O132" t="n">
+        <v>0.3612</v>
+      </c>
+      <c r="P132" t="n">
+        <v>0.35739</v>
+      </c>
+      <c r="Q132" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="R132" t="n">
+        <v>0.36017</v>
+      </c>
+      <c r="S132" t="n">
+        <v>0.36063</v>
+      </c>
+      <c r="T132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="U132" t="n">
+        <v>0.34633</v>
+      </c>
+      <c r="V132" t="n">
+        <v>0.37112</v>
+      </c>
+      <c r="W132" t="n">
+        <v>0.35881</v>
+      </c>
+      <c r="X132" t="n">
+        <v>0.35653</v>
+      </c>
+      <c r="Y132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="Z132" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="AA132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AB132" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AC132" t="n">
+        <v>0.38004</v>
+      </c>
+      <c r="AD132" t="n">
+        <v>0.35655</v>
+      </c>
+      <c r="AE132" t="n">
+        <v>0.35652</v>
+      </c>
+      <c r="AF132" t="n">
+        <v>0.35114</v>
+      </c>
+      <c r="AG132" t="n">
+        <v>0.35183</v>
+      </c>
+      <c r="AH132" t="n">
+        <v>0.35851</v>
+      </c>
+      <c r="AI132" t="n">
+        <v>0.35003</v>
+      </c>
+      <c r="AJ132" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AK132" t="n">
+        <v>0.31998</v>
+      </c>
+      <c r="AL132" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="AM132" t="n">
+        <v>0.31738</v>
+      </c>
+      <c r="AN132" t="n">
+        <v>0.26146</v>
+      </c>
+      <c r="AO132" t="n">
+        <v>0.13627</v>
+      </c>
+      <c r="AP132" t="n">
+        <v>0.29129</v>
+      </c>
+      <c r="AQ132" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="AR132" t="n">
+        <v>0.28271</v>
+      </c>
+      <c r="AS132" t="n">
+        <v>0.19531</v>
+      </c>
+      <c r="AT132" t="n">
+        <v>0.24642</v>
+      </c>
+      <c r="AU132" t="n">
+        <v>0.27857</v>
+      </c>
+      <c r="AV132" t="n">
+        <v>0.02726</v>
+      </c>
+      <c r="AW132" t="n">
+        <v>0.27962</v>
+      </c>
+      <c r="AX132" t="n">
+        <v>0.13063</v>
+      </c>
+      <c r="AY132" t="n">
+        <v>0.01859</v>
+      </c>
+      <c r="AZ132" t="n">
+        <v>0.28408</v>
+      </c>
+      <c r="BA132" t="n">
+        <v>0.23761</v>
+      </c>
+      <c r="BB132" t="n">
+        <v>0.28743</v>
+      </c>
+      <c r="BC132" t="n">
+        <v>0.24795</v>
+      </c>
+      <c r="BD132" t="n">
+        <v>0.30326</v>
+      </c>
+      <c r="BE132" t="n">
+        <v>-0.007679999999999999</v>
+      </c>
+      <c r="BF132" t="n">
+        <v>0.30525</v>
+      </c>
+      <c r="BG132" t="n">
+        <v>0.14506</v>
+      </c>
+      <c r="BH132" t="n">
+        <v>0.29969</v>
+      </c>
+      <c r="BI132" t="n">
+        <v>-0.02274</v>
+      </c>
+      <c r="BJ132" t="n">
+        <v>0.23407</v>
+      </c>
+      <c r="BK132" t="n">
+        <v>0.23687</v>
+      </c>
+      <c r="BL132" t="n">
+        <v>0.29689</v>
+      </c>
+      <c r="BM132" t="n">
+        <v>0.29759</v>
+      </c>
+      <c r="BN132" t="n">
+        <v>0.30669</v>
+      </c>
+      <c r="BO132" t="n">
+        <v>0.30361</v>
+      </c>
+      <c r="BP132" t="n">
+        <v>0.31014</v>
+      </c>
+      <c r="BQ132" t="n">
+        <v>0.29931</v>
+      </c>
+      <c r="BR132" t="n">
+        <v>0.31405</v>
+      </c>
+      <c r="BS132" t="n">
+        <v>0.33653</v>
+      </c>
+      <c r="BT132" t="n">
+        <v>0.34085</v>
+      </c>
+      <c r="BU132" t="n">
+        <v>0.34071</v>
+      </c>
+      <c r="BV132" t="n">
+        <v>0.29801</v>
+      </c>
+      <c r="BW132" t="n">
+        <v>0.34221</v>
+      </c>
+      <c r="BX132" t="n">
+        <v>0.41751</v>
+      </c>
+      <c r="BY132" t="n">
+        <v>0.36806</v>
+      </c>
+      <c r="BZ132" t="n">
+        <v>0.40872</v>
+      </c>
+      <c r="CA132" t="n">
+        <v>0.5784900000000001</v>
+      </c>
+      <c r="CB132" t="n">
+        <v>0.5620599999999999</v>
+      </c>
+      <c r="CC132" t="n">
+        <v>0.49892</v>
+      </c>
+      <c r="CD132" t="n">
+        <v>0.46226</v>
+      </c>
+      <c r="CE132" t="n">
+        <v>0.58827</v>
+      </c>
+      <c r="CF132" t="n">
+        <v>0.47796</v>
+      </c>
+      <c r="CG132" t="n">
+        <v>0.64777</v>
+      </c>
+      <c r="CH132" t="n">
+        <v>0.45389</v>
+      </c>
+      <c r="CI132" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="CJ132" t="n">
+        <v>0.4022</v>
+      </c>
+      <c r="CK132" t="n">
+        <v>0.37681</v>
+      </c>
+      <c r="CL132" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="CM132" t="n">
+        <v>0.4818</v>
+      </c>
+      <c r="CN132" t="n">
+        <v>0.4306</v>
+      </c>
+      <c r="CO132" t="n">
+        <v>0.41997</v>
+      </c>
+      <c r="CP132" t="n">
+        <v>0.37888</v>
+      </c>
+      <c r="CQ132" t="n">
+        <v>0.37491</v>
+      </c>
+      <c r="CR132" t="n">
+        <v>0.36735</v>
+      </c>
+      <c r="CS132" t="n">
+        <v>0.3602</v>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="2" t="n">
+        <v>46156</v>
+      </c>
+      <c r="B133" t="n">
+        <v>0.34697</v>
+      </c>
+      <c r="C133" t="n">
+        <v>0.49341</v>
+      </c>
+      <c r="D133" t="n">
+        <v>0.47453</v>
+      </c>
+      <c r="E133" t="n">
+        <v>0.46662</v>
+      </c>
+      <c r="F133" t="n">
+        <v>0.45759</v>
+      </c>
+      <c r="G133" t="n">
+        <v>0.42154</v>
+      </c>
+      <c r="H133" t="n">
+        <v>0.40107</v>
+      </c>
+      <c r="I133" t="n">
+        <v>0.40748</v>
+      </c>
+      <c r="J133" t="n">
+        <v>0.41398</v>
+      </c>
+      <c r="K133" t="n">
+        <v>0.4114</v>
+      </c>
+      <c r="L133" t="n">
+        <v>0.41979</v>
+      </c>
+      <c r="M133" t="n">
+        <v>0.40193</v>
+      </c>
+      <c r="N133" t="n">
+        <v>0.39827</v>
+      </c>
+      <c r="O133" t="n">
+        <v>0.41404</v>
+      </c>
+      <c r="P133" t="n">
+        <v>0.41151</v>
+      </c>
+      <c r="Q133" t="n">
+        <v>0.39428</v>
+      </c>
+      <c r="R133" t="n">
+        <v>0.38802</v>
+      </c>
+      <c r="S133" t="n">
+        <v>0.41905</v>
+      </c>
+      <c r="T133" t="n">
+        <v>0.38816</v>
+      </c>
+      <c r="U133" t="n">
+        <v>0.41725</v>
+      </c>
+      <c r="V133" t="n">
+        <v>0.39044</v>
+      </c>
+      <c r="W133" t="n">
+        <v>0.40043</v>
+      </c>
+      <c r="X133" t="n">
+        <v>0.40037</v>
+      </c>
+      <c r="Y133" t="n">
+        <v>0.41312</v>
+      </c>
+      <c r="Z133" t="n">
+        <v>0.40031</v>
+      </c>
+      <c r="AA133" t="n">
+        <v>0.45082</v>
+      </c>
+      <c r="AB133" t="n">
+        <v>0.45001</v>
+      </c>
+      <c r="AC133" t="n">
+        <v>0.56135</v>
+      </c>
+      <c r="AD133" t="n">
+        <v>0.5009400000000001</v>
+      </c>
+      <c r="AE133" t="n">
+        <v>0.45098</v>
+      </c>
+      <c r="AF133" t="n">
+        <v>0.41551</v>
+      </c>
+      <c r="AG133" t="n">
+        <v>0.41975</v>
+      </c>
+      <c r="AH133" t="n">
+        <v>0.3742</v>
+      </c>
+      <c r="AI133" t="n">
+        <v>0.32747</v>
+      </c>
+      <c r="AJ133" t="n">
+        <v>0.37071</v>
+      </c>
+      <c r="AK133" t="n">
+        <v>0.37779</v>
+      </c>
+      <c r="AL133" t="n">
+        <v>0.42726</v>
+      </c>
+      <c r="AM133" t="n">
+        <v>0.37139</v>
+      </c>
+      <c r="AN133" t="n">
+        <v>0.40426</v>
+      </c>
+      <c r="AO133" t="n">
+        <v>0.33857</v>
+      </c>
+      <c r="AP133" t="n">
+        <v>0.294</v>
+      </c>
+      <c r="AQ133" t="n">
+        <v>0.32208</v>
+      </c>
+      <c r="AR133" t="n">
+        <v>0.32555</v>
+      </c>
+      <c r="AS133" t="n">
+        <v>0.32147</v>
+      </c>
+      <c r="AT133" t="n">
+        <v>0.2803</v>
+      </c>
+      <c r="AU133" t="n">
+        <v>0.28083</v>
+      </c>
+      <c r="AV133" t="n">
+        <v>0.29395</v>
+      </c>
+      <c r="AW133" t="n">
+        <v>0.17394</v>
+      </c>
+      <c r="AX133" t="n">
+        <v>0.006059999999999999</v>
+      </c>
+      <c r="AY133" t="n">
+        <v>0.15308</v>
+      </c>
+      <c r="AZ133" t="n">
+        <v>0.04128</v>
+      </c>
+      <c r="BA133" t="n">
+        <v>0.03351</v>
+      </c>
+      <c r="BB133" t="n">
+        <v>0.295</v>
+      </c>
+      <c r="BC133" t="n">
+        <v>-0.02168</v>
+      </c>
+      <c r="BD133" t="n">
+        <v>0.16569</v>
+      </c>
+      <c r="BE133" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="BF133" t="n">
+        <v>0.18332</v>
+      </c>
+      <c r="BG133" t="n">
+        <v>0.03057</v>
+      </c>
+      <c r="BH133" t="n">
+        <v>0.10711</v>
+      </c>
+      <c r="BI133" t="n">
+        <v>0.00787</v>
+      </c>
+      <c r="BJ133" t="n">
+        <v>0.26924</v>
+      </c>
+      <c r="BK133" t="n">
+        <v>0.03583</v>
+      </c>
+      <c r="BL133" t="n">
+        <v>0.3273</v>
+      </c>
+      <c r="BM133" t="n">
+        <v>0.32723</v>
+      </c>
+      <c r="BN133" t="n">
+        <v>0.31559</v>
+      </c>
+      <c r="BO133" t="n">
+        <v>0.33275</v>
+      </c>
+      <c r="BP133" t="n">
+        <v>0.32724</v>
+      </c>
+      <c r="BQ133" t="n">
+        <v>0.33339</v>
+      </c>
+      <c r="BR133" t="n">
+        <v>0.33933</v>
+      </c>
+      <c r="BS133" t="n">
+        <v>0.33428</v>
+      </c>
+      <c r="BT133" t="n">
+        <v>0.34116</v>
+      </c>
+      <c r="BU133" t="n">
+        <v>0.34245</v>
+      </c>
+      <c r="BV133" t="n">
+        <v>0.32107</v>
+      </c>
+      <c r="BW133" t="n">
+        <v>0.35917</v>
+      </c>
+      <c r="BX133" t="n">
+        <v>0.41533</v>
+      </c>
+      <c r="BY133" t="n">
+        <v>0.48608</v>
+      </c>
+      <c r="BZ133" t="n">
+        <v>0.38038</v>
+      </c>
+      <c r="CA133" t="n">
+        <v>0.50617</v>
+      </c>
+      <c r="CB133" t="n">
+        <v>0.50843</v>
+      </c>
+      <c r="CC133" t="n">
+        <v>0.42817</v>
+      </c>
+      <c r="CD133" t="n">
+        <v>0.54128</v>
+      </c>
+      <c r="CE133" t="n">
+        <v>0.58585</v>
+      </c>
+      <c r="CF133" t="n">
+        <v>0.57345</v>
+      </c>
+      <c r="CG133" t="n">
+        <v>0.5117200000000001</v>
+      </c>
+      <c r="CH133" t="n">
+        <v>0.54822</v>
+      </c>
+      <c r="CI133" t="n">
+        <v>0.43797</v>
+      </c>
+      <c r="CJ133" t="n">
+        <v>0.44196</v>
+      </c>
+      <c r="CK133" t="n">
+        <v>0.5896699999999999</v>
+      </c>
+      <c r="CL133" t="n">
+        <v>0.55626</v>
+      </c>
+      <c r="CM133" t="n">
+        <v>0.48072</v>
+      </c>
+      <c r="CN133" t="n">
+        <v>0.5056</v>
+      </c>
+      <c r="CO133" t="n">
+        <v>0.37751</v>
+      </c>
+      <c r="CP133" t="n">
+        <v>0.32463</v>
+      </c>
+      <c r="CQ133" t="n">
+        <v>0.41772</v>
+      </c>
+      <c r="CR133" t="n">
+        <v>0.41705</v>
+      </c>
+      <c r="CS133" t="n">
+        <v>0.40881</v>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="2" t="n">
+        <v>46157</v>
+      </c>
+      <c r="B134" t="n">
+        <v>0.38664</v>
+      </c>
+      <c r="C134" t="n">
+        <v>0.44408</v>
+      </c>
+      <c r="D134" t="n">
+        <v>0.39166</v>
+      </c>
+      <c r="E134" t="n">
+        <v>0.4035899999999999</v>
+      </c>
+      <c r="F134" t="n">
+        <v>0.41146</v>
+      </c>
+      <c r="G134" t="n">
+        <v>0.39983</v>
+      </c>
+      <c r="H134" t="n">
+        <v>0.39511</v>
+      </c>
+      <c r="I134" t="n">
+        <v>0.42626</v>
+      </c>
+      <c r="J134" t="n">
+        <v>0.39036</v>
+      </c>
+      <c r="K134" t="n">
+        <v>0.38188</v>
+      </c>
+      <c r="L134" t="n">
+        <v>0.41622</v>
+      </c>
+      <c r="M134" t="n">
+        <v>0.38119</v>
+      </c>
+      <c r="N134" t="n">
+        <v>0.38546</v>
+      </c>
+      <c r="O134" t="n">
+        <v>0.3809</v>
+      </c>
+      <c r="P134" t="n">
+        <v>0.37654</v>
+      </c>
+      <c r="Q134" t="n">
+        <v>0.38131</v>
+      </c>
+      <c r="R134" t="n">
+        <v>0.37615</v>
+      </c>
+      <c r="S134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="T134" t="n">
+        <v>0.35691</v>
+      </c>
+      <c r="U134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="V134" t="n">
+        <v>0.3772</v>
+      </c>
+      <c r="W134" t="n">
+        <v>0.37135</v>
+      </c>
+      <c r="X134" t="n">
+        <v>0.36028</v>
+      </c>
+      <c r="Y134" t="n">
+        <v>0.36001</v>
+      </c>
+      <c r="Z134" t="n">
+        <v>0.36589</v>
+      </c>
+      <c r="AA134" t="n">
+        <v>0.38703</v>
+      </c>
+      <c r="AB134" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="AC134" t="n">
+        <v>0.37991</v>
+      </c>
+      <c r="AD134" t="n">
+        <v>0.36675</v>
+      </c>
+      <c r="AE134" t="n">
+        <v>0.36156</v>
+      </c>
+      <c r="AF134" t="n">
+        <v>0.35526</v>
+      </c>
+      <c r="AG134" t="n">
+        <v>0.37995</v>
+      </c>
+      <c r="AH134" t="n">
+        <v>0.39982</v>
+      </c>
+      <c r="AI134" t="n">
+        <v>0.36754</v>
+      </c>
+      <c r="AJ134" t="n">
+        <v>0.37918</v>
+      </c>
+      <c r="AK134" t="n">
+        <v>0.37517</v>
+      </c>
+      <c r="AL134" t="n">
+        <v>0.39463</v>
+      </c>
+      <c r="AM134" t="n">
+        <v>0.38684</v>
+      </c>
+      <c r="AN134" t="n">
+        <v>0.35165</v>
+      </c>
+      <c r="AO134" t="n">
+        <v>0.35024</v>
+      </c>
+      <c r="AP134" t="n">
+        <v>0.34272</v>
+      </c>
+      <c r="AQ134" t="n">
+        <v>0.32649</v>
+      </c>
+      <c r="AR134" t="n">
+        <v>0.27915</v>
+      </c>
+      <c r="AS134" t="n">
+        <v>0.29585</v>
+      </c>
+      <c r="AT134" t="n">
+        <v>0.1585</v>
+      </c>
+      <c r="AU134" t="n">
+        <v>0.34463</v>
+      </c>
+      <c r="AV134" t="n">
+        <v>0.27321</v>
+      </c>
+      <c r="AW134" t="n">
+        <v>0.3479</v>
+      </c>
+      <c r="AX134" t="n">
+        <v>-0.03817</v>
+      </c>
+      <c r="AY134" t="n">
+        <v>0.31229</v>
+      </c>
+      <c r="AZ134" t="n">
+        <v>0.35161</v>
+      </c>
+      <c r="BA134" t="n">
+        <v>0.40848</v>
+      </c>
+      <c r="BB134" t="n">
+        <v>0.37351</v>
+      </c>
+      <c r="BC134" t="n">
+        <v>0.45292</v>
+      </c>
+      <c r="BD134" t="n">
+        <v>0.40863</v>
+      </c>
+      <c r="BE134" t="n">
+        <v>0.4639</v>
+      </c>
+      <c r="BF134" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="BG134" t="n">
+        <v>0.30802</v>
+      </c>
+      <c r="BH134" t="n">
+        <v>-0.01515</v>
+      </c>
+      <c r="BI134" t="n">
+        <v>0.18512</v>
+      </c>
+      <c r="BJ134" t="n">
+        <v>0.30465</v>
+      </c>
+      <c r="BK134" t="n">
+        <v>0.2909</v>
+      </c>
+      <c r="BL134" t="n">
+        <v>0.31564</v>
+      </c>
+      <c r="BM134" t="n">
+        <v>0.35238</v>
+      </c>
+      <c r="BN134" t="n">
+        <v>0.35053</v>
+      </c>
+      <c r="BO134" t="n">
+        <v>0.34793</v>
+      </c>
+      <c r="BP134" t="n">
+        <v>0.34861</v>
+      </c>
+      <c r="BQ134" t="n">
+        <v>0.3651</v>
+      </c>
+      <c r="BR134" t="n">
+        <v>0.36243</v>
+      </c>
+      <c r="BS134" t="n">
+        <v>0.35609</v>
+      </c>
+      <c r="BT134" t="n">
+        <v>0.38612</v>
+      </c>
+      <c r="BU134" t="n">
+        <v>0.38487</v>
+      </c>
+      <c r="BV134" t="n">
+        <v>0.35795</v>
+      </c>
+      <c r="BW134" t="n">
+        <v>0.38721</v>
+      </c>
+      <c r="BX134" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="BY134" t="n">
+        <v>0.37488</v>
+      </c>
+      <c r="BZ134" t="n">
+        <v>0.36262</v>
+      </c>
+      <c r="CA134" t="n">
+        <v>0.35448</v>
+      </c>
+      <c r="CB134" t="n">
+        <v>0.37324</v>
+      </c>
+      <c r="CC134" t="n">
+        <v>0.37287</v>
+      </c>
+      <c r="CD134" t="n">
+        <v>0.3888</v>
+      </c>
+      <c r="CE134" t="n">
+        <v>0.39521</v>
+      </c>
+      <c r="CF134" t="n">
+        <v>0.34262</v>
+      </c>
+      <c r="CG134" t="n">
+        <v>0.36036</v>
+      </c>
+      <c r="CH134" t="n">
+        <v>0.37028</v>
+      </c>
+      <c r="CI134" t="n">
+        <v>0.40119</v>
+      </c>
+      <c r="CJ134" t="n">
+        <v>0.36011</v>
+      </c>
+      <c r="CK134" t="n">
+        <v>0.37004</v>
+      </c>
+      <c r="CL134" t="n">
+        <v>0.35511</v>
+      </c>
+      <c r="CM134" t="n">
+        <v>0.38021</v>
+      </c>
+      <c r="CN134" t="n">
+        <v>0.38074</v>
+      </c>
+      <c r="CO134" t="n">
+        <v>0.36773</v>
+      </c>
+      <c r="CP134" t="n">
+        <v>0.36062</v>
+      </c>
+      <c r="CQ134" t="n">
+        <v>0.3778</v>
+      </c>
+      <c r="CR134" t="n">
+        <v>0.37034</v>
+      </c>
+      <c r="CS134" t="n">
+        <v>0.36274</v>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="2" t="n">
+        <v>46158</v>
+      </c>
+      <c r="B135" t="n">
+        <v>0.3323</v>
+      </c>
+      <c r="C135" t="n">
+        <v>0.4438</v>
+      </c>
+      <c r="D135" t="n">
+        <v>0.35699</v>
+      </c>
+      <c r="E135" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="F135" t="n">
+        <v>0.37792</v>
+      </c>
+      <c r="G135" t="n">
+        <v>0.61277</v>
+      </c>
+      <c r="H135" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="I135" t="n">
+        <v>0.3544</v>
+      </c>
+      <c r="J135" t="n">
+        <v>0.35121</v>
+      </c>
+      <c r="K135" t="n">
+        <v>0.64585</v>
+      </c>
+      <c r="L135" t="n">
+        <v>0.32241</v>
+      </c>
+      <c r="M135" t="n">
+        <v>0.32765</v>
+      </c>
+      <c r="N135" t="n">
+        <v>0.38401</v>
+      </c>
+      <c r="O135" t="n">
+        <v>0.32465</v>
+      </c>
+      <c r="P135" t="n">
+        <v>0.3913</v>
+      </c>
+      <c r="Q135" t="n">
+        <v>0.35211</v>
+      </c>
+      <c r="R135" t="n">
+        <v>0.34371</v>
+      </c>
+      <c r="S135" t="n">
+        <v>0.33177</v>
+      </c>
+      <c r="T135" t="n">
+        <v>0.33165</v>
+      </c>
+      <c r="U135" t="n">
+        <v>0.33503</v>
+      </c>
+      <c r="V135" t="n">
+        <v>0.34053</v>
+      </c>
+      <c r="W135" t="n">
+        <v>0.33565</v>
+      </c>
+      <c r="X135" t="n">
+        <v>0.34066</v>
+      </c>
+      <c r="Y135" t="n">
+        <v>0.34567</v>
+      </c>
+      <c r="Z135" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="AA135" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="AB135" t="n">
+        <v>0.34366</v>
+      </c>
+      <c r="AC135" t="n">
+        <v>0.34375</v>
+      </c>
+      <c r="AD135" t="n">
+        <v>0.3499</v>
+      </c>
+      <c r="AE135" t="n">
+        <v>0.3311</v>
+      </c>
+      <c r="AF135" t="n">
+        <v>0.32191</v>
+      </c>
+      <c r="AG135" t="n">
+        <v>0.31617</v>
+      </c>
+      <c r="AH135" t="n">
+        <v>0.33002</v>
+      </c>
+      <c r="AI135" t="n">
+        <v>0.24866</v>
+      </c>
+      <c r="AJ135" t="n">
+        <v>0.33216</v>
+      </c>
+      <c r="AK135" t="n">
+        <v>0.32665</v>
+      </c>
+      <c r="AL135" t="n">
+        <v>0.32093</v>
+      </c>
+      <c r="AM135" t="n">
+        <v>0.23551</v>
+      </c>
+      <c r="AN135" t="n">
+        <v>0.29825</v>
+      </c>
+      <c r="AO135" t="n">
+        <v>0.23722</v>
+      </c>
+      <c r="AP135" t="n">
+        <v>0.24627</v>
+      </c>
+      <c r="AQ135" t="n">
+        <v>0.25197</v>
+      </c>
+      <c r="AR135" t="n">
+        <v>0.03936</v>
+      </c>
+      <c r="AS135" t="n">
+        <v>0.04005</v>
+      </c>
+      <c r="AT135" t="n">
+        <v>0.14807</v>
+      </c>
+      <c r="AU135" t="n">
+        <v>0.29403</v>
+      </c>
+      <c r="AV135" t="n">
+        <v>0.05636</v>
+      </c>
+      <c r="AW135" t="n">
+        <v>0.17591</v>
+      </c>
+      <c r="AX135" t="n">
+        <v>0.04341</v>
+      </c>
+      <c r="AY135" t="n">
+        <v>0.25944</v>
+      </c>
+      <c r="AZ135" t="n">
+        <v>0.03954</v>
+      </c>
+      <c r="BA135" t="n">
+        <v>0.1486</v>
+      </c>
+      <c r="BB135" t="n">
+        <v>0.15242</v>
+      </c>
+      <c r="BC135" t="n">
+        <v>0.05869</v>
+      </c>
+      <c r="BD135" t="n">
+        <v>0.30103</v>
+      </c>
+      <c r="BE135" t="n">
+        <v>0.00929</v>
+      </c>
+      <c r="BF135" t="n">
+        <v>0.12188</v>
+      </c>
+      <c r="BG135" t="n">
+        <v>0.04477</v>
+      </c>
+      <c r="BH135" t="n">
+        <v>-0.04382</v>
+      </c>
+      <c r="BI135" t="n">
+        <v>-0.03112</v>
+      </c>
+      <c r="BJ135" t="n">
+        <v>0.14865</v>
+      </c>
+      <c r="BK135" t="n">
+        <v>0.28364</v>
+      </c>
+      <c r="BL135" t="n">
+        <v>-0.02918</v>
+      </c>
+      <c r="BM135" t="n">
+        <v>-0.01234</v>
+      </c>
+      <c r="BN135" t="n">
+        <v>0.30193</v>
+      </c>
+      <c r="BO135" t="n">
+        <v>0.03255</v>
+      </c>
+      <c r="BP135" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="BQ135" t="n">
+        <v>0.32244</v>
+      </c>
+      <c r="BR135" t="n">
+        <v>0.32659</v>
+      </c>
+      <c r="BS135" t="n">
+        <v>0.32237</v>
+      </c>
+      <c r="BT135" t="n">
+        <v>0.34512</v>
+      </c>
+      <c r="BU135" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BV135" t="n">
+        <v>0.33099</v>
+      </c>
+      <c r="BW135" t="n">
+        <v>0.3363</v>
+      </c>
+      <c r="BX135" t="n">
+        <v>0.35038</v>
+      </c>
+      <c r="BY135" t="n">
+        <v>0.34335</v>
+      </c>
+      <c r="BZ135" t="n">
+        <v>0.30905</v>
+      </c>
+      <c r="CA135" t="n">
+        <v>0.35072</v>
+      </c>
+      <c r="CB135" t="n">
+        <v>0.35472</v>
+      </c>
+      <c r="CC135" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="CD135" t="n">
+        <v>0.35459</v>
+      </c>
+      <c r="CE135" t="n">
+        <v>0.36201</v>
+      </c>
+      <c r="CF135" t="n">
+        <v>0.36426</v>
+      </c>
+      <c r="CG135" t="n">
+        <v>0.35963</v>
+      </c>
+      <c r="CH135" t="n">
+        <v>0.34484</v>
+      </c>
+      <c r="CI135" t="n">
+        <v>0.35977</v>
+      </c>
+      <c r="CJ135" t="n">
+        <v>0.37417</v>
+      </c>
+      <c r="CK135" t="n">
+        <v>0.34451</v>
+      </c>
+      <c r="CL135" t="n">
+        <v>0.36731</v>
+      </c>
+      <c r="CM135" t="n">
+        <v>0.37174</v>
+      </c>
+      <c r="CN135" t="n">
+        <v>0.3607</v>
+      </c>
+      <c r="CO135" t="n">
+        <v>0.35154</v>
+      </c>
+      <c r="CP135" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="CQ135" t="n">
+        <v>0.35139</v>
+      </c>
+      <c r="CR135" t="n">
+        <v>0.35172</v>
+      </c>
+      <c r="CS135" t="n">
+        <v>0.35142</v>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="2" t="n">
+        <v>46159</v>
+      </c>
+      <c r="B136" t="n">
+        <v>0.32427</v>
+      </c>
+      <c r="C136" t="n">
+        <v>0.32572</v>
+      </c>
+      <c r="D136" t="n">
+        <v>0.33203</v>
+      </c>
+      <c r="E136" t="n">
+        <v>0.34137</v>
+      </c>
+      <c r="F136" t="n">
+        <v>0.34079</v>
+      </c>
+      <c r="G136" t="n">
+        <v>0.34111</v>
+      </c>
+      <c r="H136" t="n">
+        <v>0.33311</v>
+      </c>
+      <c r="I136" t="n">
+        <v>0.32673</v>
+      </c>
+      <c r="J136" t="n">
+        <v>0.3215</v>
+      </c>
+      <c r="K136" t="n">
+        <v>0.32154</v>
+      </c>
+      <c r="L136" t="n">
+        <v>0.31225</v>
+      </c>
+      <c r="M136" t="n">
+        <v>0.3117</v>
+      </c>
+      <c r="N136" t="n">
+        <v>0.31647</v>
+      </c>
+      <c r="O136" t="n">
+        <v>0.31079</v>
+      </c>
+      <c r="P136" t="n">
+        <v>0.31262</v>
+      </c>
+      <c r="Q136" t="n">
+        <v>0.31144</v>
+      </c>
+      <c r="R136" t="n">
+        <v>0.3112799999999999</v>
+      </c>
+      <c r="S136" t="n">
+        <v>0.32146</v>
+      </c>
+      <c r="T136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="U136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="V136" t="n">
+        <v>0.30982</v>
+      </c>
+      <c r="W136" t="n">
+        <v>0.31364</v>
+      </c>
+      <c r="X136" t="n">
+        <v>0.30663</v>
+      </c>
+      <c r="Y136" t="n">
+        <v>0.30727</v>
+      </c>
+      <c r="Z136" t="n">
+        <v>0.308</v>
+      </c>
+      <c r="AA136" t="n">
+        <v>0.31087</v>
+      </c>
+      <c r="AB136" t="n">
+        <v>0.31197</v>
+      </c>
+      <c r="AC136" t="n">
+        <v>0.29153</v>
+      </c>
+      <c r="AD136" t="n">
+        <v>0.19286</v>
+      </c>
+      <c r="AE136" t="n">
+        <v>0.18666</v>
+      </c>
+      <c r="AF136" t="n">
+        <v>0.13129</v>
+      </c>
+      <c r="AG136" t="n">
+        <v>0.15013</v>
+      </c>
+      <c r="AH136" t="n">
+        <v>0.04681</v>
+      </c>
+      <c r="AI136" t="n">
+        <v>0.01616</v>
+      </c>
+      <c r="AJ136" t="n">
+        <v>-0.0015</v>
+      </c>
+      <c r="AK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AM136" t="n">
+        <v>0.04365</v>
+      </c>
+      <c r="AN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO136" t="n">
+        <v>-0.04148</v>
+      </c>
+      <c r="AP136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AQ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AR136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AS136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AU136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BC136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BE136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BG136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BL136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BM136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BN136" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BO136" t="n">
+        <v>0.13904</v>
+      </c>
+      <c r="BP136" t="n">
+        <v>0.19113</v>
+      </c>
+      <c r="BQ136" t="n">
+        <v>0.27689</v>
+      </c>
+      <c r="BR136" t="n">
+        <v>0.22334</v>
+      </c>
+      <c r="BS136" t="n">
+        <v>0.22398</v>
+      </c>
+      <c r="BT136" t="n">
+        <v>0.22483</v>
+      </c>
+      <c r="BU136" t="n">
+        <v>0.22908</v>
+      </c>
+      <c r="BV136" t="n">
+        <v>0.23941</v>
+      </c>
+      <c r="BW136" t="n">
+        <v>0.26624</v>
+      </c>
+      <c r="BX136" t="n">
+        <v>0.24905</v>
+      </c>
+      <c r="BY136" t="n">
+        <v>0.24238</v>
+      </c>
+      <c r="BZ136" t="n">
+        <v>0.2336</v>
+      </c>
+      <c r="CA136" t="n">
+        <v>0.29804</v>
+      </c>
+      <c r="CB136" t="n">
+        <v>0.24956</v>
+      </c>
+      <c r="CC136" t="n">
+        <v>0.25321</v>
+      </c>
+      <c r="CD136" t="n">
+        <v>0.23607</v>
+      </c>
+      <c r="CE136" t="n">
+        <v>0.25439</v>
+      </c>
+      <c r="CF136" t="n">
+        <v>0.243</v>
+      </c>
+      <c r="CG136" t="n">
+        <v>0.2604</v>
+      </c>
+      <c r="CH136" t="n">
+        <v>0.24832</v>
+      </c>
+      <c r="CI136" t="n">
+        <v>0.26164</v>
+      </c>
+      <c r="CJ136" t="n">
+        <v>0.32113</v>
+      </c>
+      <c r="CK136" t="n">
+        <v>0.27591</v>
+      </c>
+      <c r="CL136" t="n">
+        <v>0.27601</v>
+      </c>
+      <c r="CM136" t="n">
+        <v>0.25863</v>
+      </c>
+      <c r="CN136" t="n">
+        <v>0.21811</v>
+      </c>
+      <c r="CO136" t="n">
+        <v>0.23843</v>
+      </c>
+      <c r="CP136" t="n">
+        <v>0.21635</v>
+      </c>
+      <c r="CQ136" t="n">
+        <v>0.18605</v>
+      </c>
+      <c r="CR136" t="n">
+        <v>0.08489000000000001</v>
+      </c>
+      <c r="CS136" t="n">
+        <v>-0.03792</v>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="2" t="n">
+        <v>46160</v>
+      </c>
+      <c r="B137" t="n">
+        <v>0.29795</v>
+      </c>
+      <c r="C137" t="n">
+        <v>0.23946</v>
+      </c>
+      <c r="D137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="E137" t="n">
+        <v>-0.04503</v>
+      </c>
+      <c r="F137" t="n">
+        <v>0.15617</v>
+      </c>
+      <c r="G137" t="n">
+        <v>0.15678</v>
+      </c>
+      <c r="H137" t="n">
+        <v>0.15713</v>
+      </c>
+      <c r="I137" t="n">
+        <v>0.02409</v>
+      </c>
+      <c r="J137" t="n">
+        <v>0.23376</v>
+      </c>
+      <c r="K137" t="n">
+        <v>0.2178</v>
+      </c>
+      <c r="L137" t="n">
+        <v>0.20149</v>
+      </c>
+      <c r="M137" t="n">
+        <v>0.1655</v>
+      </c>
+      <c r="N137" t="n">
+        <v>0.15838</v>
+      </c>
+      <c r="O137" t="n">
+        <v>0.13259</v>
+      </c>
+      <c r="P137" t="n">
+        <v>0.15806</v>
+      </c>
+      <c r="Q137" t="n">
+        <v>0.18859</v>
+      </c>
+      <c r="R137" t="n">
+        <v>0.10966</v>
+      </c>
+      <c r="S137" t="n">
+        <v>0.125</v>
+      </c>
+      <c r="T137" t="n">
+        <v>0.19119</v>
+      </c>
+      <c r="U137" t="n">
+        <v>0.16035</v>
+      </c>
+      <c r="V137" t="n">
+        <v>0.21072</v>
+      </c>
+      <c r="W137" t="n">
+        <v>0.18333</v>
+      </c>
+      <c r="X137" t="n">
+        <v>0.17114</v>
+      </c>
+      <c r="Y137" t="n">
+        <v>0.2227</v>
+      </c>
+      <c r="Z137" t="n">
+        <v>0.17069</v>
+      </c>
+      <c r="AA137" t="n">
+        <v>0.22159</v>
+      </c>
+      <c r="AB137" t="n">
+        <v>0.29104</v>
+      </c>
+      <c r="AC137" t="n">
+        <v>0.22862</v>
+      </c>
+      <c r="AD137" t="n">
+        <v>0.21049</v>
+      </c>
+      <c r="AE137" t="n">
+        <v>0.2174</v>
+      </c>
+      <c r="AF137" t="n">
+        <v>0.13123</v>
+      </c>
+      <c r="AG137" t="n">
+        <v>-0.04227</v>
+      </c>
+      <c r="AH137" t="n">
+        <v>0.34196</v>
+      </c>
+      <c r="AI137" t="n">
+        <v>0.34642</v>
+      </c>
+      <c r="AJ137" t="n">
+        <v>0.44417</v>
+      </c>
+      <c r="AK137" t="n">
+        <v>0.19765</v>
+      </c>
+      <c r="AL137" t="n">
+        <v>0.00034</v>
+      </c>
+      <c r="AM137" t="n">
+        <v>0.17142</v>
+      </c>
+      <c r="AN137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AO137" t="n">
+        <v>0.16761</v>
+      </c>
+      <c r="AP137" t="n">
+        <v>0.01073</v>
+      </c>
+      <c r="AQ137" t="n">
+        <v>-0.04546</v>
+      </c>
+      <c r="AR137" t="n">
+        <v>-0.02371</v>
+      </c>
+      <c r="AS137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT137" t="n">
+        <v>0.18708</v>
+      </c>
+      <c r="AU137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV137" t="n">
+        <v>0.26641</v>
+      </c>
+      <c r="AW137" t="n">
+        <v>-0.04923</v>
+      </c>
+      <c r="AX137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AY137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AZ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BA137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BB137" t="n">
+        <v>0.08148999999999999</v>
+      </c>
+      <c r="BC137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BD137" t="n">
+        <v>-0.04679</v>
+      </c>
+      <c r="BE137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BF137" t="n">
+        <v>0.01333</v>
+      </c>
+      <c r="BG137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BH137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BI137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BJ137" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="BK137" t="n">
+        <v>-0.04706</v>
+      </c>
+      <c r="BL137" t="n">
+        <v>0.23482</v>
+      </c>
+      <c r="BM137" t="n">
+        <v>0.28068</v>
+      </c>
+      <c r="BN137" t="n">
+        <v>0.25259</v>
+      </c>
+      <c r="BO137" t="n">
+        <v>0.28211</v>
+      </c>
+      <c r="BP137" t="n">
+        <v>0.30586</v>
+      </c>
+      <c r="BQ137" t="n">
+        <v>0.30756</v>
+      </c>
+      <c r="BR137" t="n">
+        <v>0.30385</v>
+      </c>
+      <c r="BS137" t="n">
+        <v>0.31962</v>
+      </c>
+      <c r="BT137" t="n">
+        <v>0.32266</v>
+      </c>
+      <c r="BU137" t="n">
+        <v>0.3123</v>
+      </c>
+      <c r="BV137" t="n">
+        <v>0.31651</v>
+      </c>
+      <c r="BW137" t="n">
+        <v>0.33068</v>
+      </c>
+      <c r="BX137" t="n">
+        <v>0.32529</v>
+      </c>
+      <c r="BY137" t="n">
+        <v>0.34464</v>
+      </c>
+      <c r="BZ137" t="n">
+        <v>0.33108</v>
+      </c>
+      <c r="CA137" t="n">
+        <v>0.34645</v>
+      </c>
+      <c r="CB137" t="n">
+        <v>0.35096</v>
+      </c>
+      <c r="CC137" t="n">
+        <v>0.19784</v>
+      </c>
+      <c r="CD137" t="n">
+        <v>0.34529</v>
+      </c>
+      <c r="CE137" t="n">
+        <v>0.34508</v>
+      </c>
+      <c r="CF137" t="n">
+        <v>0.33792</v>
+      </c>
+      <c r="CG137" t="n">
+        <v>0.35259</v>
+      </c>
+      <c r="CH137" t="n">
+        <v>0.34401</v>
+      </c>
+      <c r="CI137" t="n">
+        <v>0.3689</v>
+      </c>
+      <c r="CJ137" t="n">
+        <v>0.33492</v>
+      </c>
+      <c r="CK137" t="n">
+        <v>0.34537</v>
+      </c>
+      <c r="CL137" t="n">
+        <v>0.35483</v>
+      </c>
+      <c r="CM137" t="n">
+        <v>0.32226</v>
+      </c>
+      <c r="CN137" t="n">
+        <v>0.33018</v>
+      </c>
+      <c r="CO137" t="n">
+        <v>0.33073</v>
+      </c>
+      <c r="CP137" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="CQ137" t="n">
+        <v>0.32934</v>
+      </c>
+      <c r="CR137" t="n">
+        <v>0.3408</v>
+      </c>
+      <c r="CS137" t="n">
+        <v>0.32626</v>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="2" t="n">
+        <v>46161</v>
+      </c>
+      <c r="B138" t="n">
+        <v>0.33029</v>
+      </c>
+      <c r="C138" t="n">
+        <v>0.35537</v>
+      </c>
+      <c r="D138" t="n">
+        <v>0.36872</v>
+      </c>
+      <c r="E138" t="n">
+        <v>0.33583</v>
+      </c>
+      <c r="F138" t="n">
+        <v>0.33788</v>
+      </c>
+      <c r="G138" t="n">
+        <v>0.33695</v>
+      </c>
+      <c r="H138" t="n">
+        <v>0.33107</v>
+      </c>
+      <c r="I138" t="n">
+        <v>0.33105</v>
+      </c>
+      <c r="J138" t="n">
+        <v>0.33126</v>
+      </c>
+      <c r="K138" t="n">
+        <v>0.33104</v>
+      </c>
+      <c r="L138" t="n">
+        <v>0.32927</v>
+      </c>
+      <c r="M138" t="n">
+        <v>0.34042</v>
+      </c>
+      <c r="N138" t="n">
+        <v>0.32995</v>
+      </c>
+      <c r="O138" t="n">
+        <v>0.33125</v>
+      </c>
+      <c r="P138" t="n">
+        <v>0.32732</v>
+      </c>
+      <c r="Q138" t="n">
+        <v>0.34455</v>
+      </c>
+      <c r="R138" t="n">
+        <v>0.1057</v>
+      </c>
+      <c r="S138" t="n">
+        <v>0.32169</v>
+      </c>
+      <c r="T138" t="n">
+        <v>0.32708</v>
+      </c>
+      <c r="U138" t="n">
+        <v>0.32098</v>
+      </c>
+      <c r="V138" t="n">
+        <v>0.33141</v>
+      </c>
+      <c r="W138" t="n">
+        <v>0.3286</v>
+      </c>
+      <c r="X138" t="n">
+        <v>0.32227</v>
+      </c>
+      <c r="Y138" t="n">
+        <v>0.33182</v>
+      </c>
+      <c r="Z138" t="n">
+        <v>0.33284</v>
+      </c>
+      <c r="AA138" t="n">
+        <v>0.33961</v>
+      </c>
+      <c r="AB138" t="n">
+        <v>0.27245</v>
+      </c>
+      <c r="AC138" t="n">
+        <v>0.43714</v>
+      </c>
+      <c r="AD138" t="n">
+        <v>0.25905</v>
+      </c>
+      <c r="AE138" t="n">
+        <v>0.31563</v>
+      </c>
+      <c r="AF138" t="n">
+        <v>0.2539</v>
+      </c>
+      <c r="AG138" t="n">
+        <v>0.11958</v>
+      </c>
+      <c r="AH138" t="n">
+        <v>0.24357</v>
+      </c>
+      <c r="AI138" t="n">
+        <v>0.32577</v>
+      </c>
+      <c r="AJ138" t="n">
+        <v>0.30479</v>
+      </c>
+      <c r="AK138" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="AL138" t="n">
+        <v>0.39695</v>
+      </c>
+      <c r="AM138" t="n">
+        <v>0.29478</v>
+      </c>
+      <c r="AN138" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="AO138" t="n">
+        <v>0.29633</v>
+      </c>
+      <c r="AP138" t="n">
+        <v>0.33028</v>
+      </c>
+      <c r="AQ138" t="n">
+        <v>0.30135</v>
+      </c>
+      <c r="AR138" t="n">
+        <v>0.29947</v>
+      </c>
+      <c r="AS138" t="n">
+        <v>0.30117</v>
+      </c>
+      <c r="AT138" t="n">
+        <v>0.31296</v>
+      </c>
+      <c r="AU138" t="n">
+        <v>0.30979</v>
+      </c>
+      <c r="AV138" t="n">
+        <v>0.31031</v>
+      </c>
+      <c r="AW138" t="n">
+        <v>0.29312</v>
+      </c>
+      <c r="AX138" t="n">
+        <v>-0.00351</v>
+      </c>
+      <c r="AY138" t="n">
+        <v>0.25658</v>
+      </c>
+      <c r="AZ138" t="n">
+        <v>0.26982</v>
+      </c>
+      <c r="BA138" t="n">
+        <v>0.3042</v>
+      </c>
+      <c r="BB138" t="n">
+        <v>0.31206</v>
+      </c>
+      <c r="BC138" t="n">
+        <v>0.18918</v>
+      </c>
+      <c r="BD138" t="n">
+        <v>0.31891</v>
+      </c>
+      <c r="BE138" t="n">
+        <v>0.31264</v>
+      </c>
+      <c r="BF138" t="n">
+        <v>0.14346</v>
+      </c>
+      <c r="BG138" t="n">
+        <v>0.10531</v>
+      </c>
+      <c r="BH138" t="n">
+        <v>0.30853</v>
+      </c>
+      <c r="BI138" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="BJ138" t="n">
+        <v>0.30978</v>
+      </c>
+      <c r="BK138" t="n">
+        <v>0.316</v>
+      </c>
+      <c r="BL138" t="n">
+        <v>0.32104</v>
+      </c>
+      <c r="BM138" t="n">
+        <v>0.32647</v>
+      </c>
+      <c r="BN138" t="n">
+        <v>0.33931</v>
+      </c>
+      <c r="BO138" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="BP138" t="n">
+        <v>0.34689</v>
+      </c>
+      <c r="BQ138" t="n">
+        <v>0.34088</v>
+      </c>
+      <c r="BR138" t="n">
+        <v>0.3284</v>
+      </c>
+      <c r="BS138" t="n">
+        <v>0.34017</v>
+      </c>
+      <c r="BT138" t="n">
+        <v>0.3419</v>
+      </c>
+      <c r="BU138" t="n">
+        <v>0.34622</v>
+      </c>
+      <c r="BV138" t="n">
+        <v>0.33304</v>
+      </c>
+      <c r="BW138" t="n">
+        <v>0.34926</v>
+      </c>
+      <c r="BX138" t="n">
+        <v>0.34809</v>
+      </c>
+      <c r="BY138" t="n">
+        <v>0.33816</v>
+      </c>
+      <c r="BZ138" t="n">
+        <v>0.34756</v>
+      </c>
+      <c r="CA138" t="n">
+        <v>0.35316</v>
+      </c>
+      <c r="CB138" t="n">
+        <v>0.3496</v>
+      </c>
+      <c r="CC138" t="n">
+        <v>0.37271</v>
+      </c>
+      <c r="CD138" t="n">
+        <v>0.31091</v>
+      </c>
+      <c r="CE138" t="n">
+        <v>0.32947</v>
+      </c>
+      <c r="CF138" t="n">
+        <v>0.35171</v>
+      </c>
+      <c r="CG138" t="n">
+        <v>0.39614</v>
+      </c>
+      <c r="CH138" t="n">
+        <v>0.34958</v>
+      </c>
+      <c r="CI138" t="n">
+        <v>0.36618</v>
+      </c>
+      <c r="CJ138" t="n">
+        <v>0.33863</v>
+      </c>
+      <c r="CK138" t="n">
+        <v>0.36219</v>
+      </c>
+      <c r="CL138" t="n">
+        <v>0.34999</v>
+      </c>
+      <c r="CM138" t="n">
+        <v>0.36896</v>
+      </c>
+      <c r="CN138" t="n">
+        <v>0.3542</v>
+      </c>
+      <c r="CO138" t="n">
+        <v>0.31735</v>
+      </c>
+      <c r="CP138" t="n">
+        <v>0.33318</v>
+      </c>
+      <c r="CQ138" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="CR138" t="n">
+        <v>0.3316</v>
+      </c>
+      <c r="CS138" t="n">
+        <v>0.33214</v>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="2" t="n">
+        <v>46162</v>
+      </c>
+      <c r="B139" t="n">
+        <v>0.3271</v>
+      </c>
+      <c r="C139" t="n">
+        <v>0.36533</v>
+      </c>
+      <c r="D139" t="n">
+        <v>0.33113</v>
+      </c>
+      <c r="E139" t="n">
+        <v>0.33111</v>
+      </c>
+      <c r="F139" t="n">
+        <v>0.24093</v>
+      </c>
+      <c r="G139" t="n">
+        <v>0.31653</v>
+      </c>
+      <c r="H139" t="n">
+        <v>0.32026</v>
+      </c>
+      <c r="I139" t="n">
+        <v>0.32017</v>
+      </c>
+      <c r="J139" t="n">
+        <v>0.32933</v>
+      </c>
+      <c r="K139" t="n">
+        <v>0.33079</v>
+      </c>
+      <c r="L139" t="n">
+        <v>0.33102</v>
+      </c>
+      <c r="M139" t="n">
+        <v>0.32967</v>
+      </c>
+      <c r="N139" t="n">
+        <v>0.34524</v>
+      </c>
+      <c r="O139" t="n">
+        <v>0.26398</v>
+      </c>
+      <c r="P139" t="n">
+        <v>0.34963</v>
+      </c>
+      <c r="Q139" t="n">
+        <v>0.34124</v>
+      </c>
+      <c r="R139" t="n">
+        <v>0.33625</v>
+      </c>
+      <c r="S139" t="n">
+        <v>0.32099</v>
+      </c>
+      <c r="T139" t="n">
+        <v>0.32073</v>
+      </c>
+      <c r="U139" t="n">
+        <v>0.33117</v>
+      </c>
+      <c r="V139" t="n">
+        <v>0.34664</v>
+      </c>
+      <c r="W139" t="n">
+        <v>0.33127</v>
+      </c>
+      <c r="X139" t="n">
+        <v>0.34038</v>
+      </c>
+      <c r="Y139" t="n">
+        <v>0.35303</v>
+      </c>
+      <c r="Z139" t="n">
+        <v>0.32339</v>
+      </c>
+      <c r="AA139" t="n">
+        <v>0.37624</v>
+      </c>
+      <c r="AB139" t="n">
+        <v>0.35546</v>
+      </c>
+      <c r="AC139" t="n">
+        <v>0.3829</v>
+      </c>
+      <c r="AD139" t="n">
+        <v>0.36362</v>
+      </c>
+      <c r="AE139" t="n">
+        <v>0.34887</v>
+      </c>
+      <c r="AF139" t="n">
+        <v>0.27602</v>
+      </c>
+      <c r="AG139" t="n">
+        <v>0.33011</v>
+      </c>
+      <c r="AH139" t="n">
+        <v>0.34224</v>
+      </c>
+      <c r="AI139" t="n">
+        <v>0.3069</v>
+      </c>
+      <c r="AJ139" t="n">
+        <v>0.23547</v>
+      </c>
+      <c r="AK139" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AL139" t="n">
+        <v>0.25898</v>
+      </c>
+      <c r="AM139" t="n">
+        <v>0.25591</v>
+      </c>
+      <c r="AN139" t="n">
+        <v>0.31784</v>
+      </c>
+      <c r="AO139" t="n">
+        <v>0.31746</v>
+      </c>
+      <c r="AP139" t="n">
+        <v>0.34602</v>
+      </c>
+      <c r="AQ139" t="n">
+        <v>0.29606</v>
+      </c>
+      <c r="AR139" t="n">
+        <v>0.27391</v>
+      </c>
+      <c r="AS139" t="n">
+        <v>0.2838</v>
+      </c>
+      <c r="AT139" t="n">
+        <v>0.28202</v>
+      </c>
+      <c r="AU139" t="n">
+        <v>0.26741</v>
+      </c>
+      <c r="AV139" t="n">
+        <v>0.17454</v>
+      </c>
+      <c r="AW139" t="n">
+        <v>0.26158</v>
+      </c>
+      <c r="AX139" t="n">
+        <v>0.30794</v>
+      </c>
+      <c r="AY139" t="n">
+        <v>0.38448</v>
+      </c>
+      <c r="AZ139" t="n">
+        <v>0.26549</v>
+      </c>
+      <c r="BA139" t="n">
+        <v>0.26679</v>
+      </c>
+      <c r="BB139" t="n">
+        <v>0.26314</v>
+      </c>
+      <c r="BC139" t="n">
+        <v>0.29293</v>
+      </c>
+      <c r="BD139" t="n">
+        <v>0.34634</v>
+      </c>
+      <c r="BE139" t="n">
+        <v>0.32836</v>
+      </c>
+      <c r="BF139" t="n">
+        <v>0.32905</v>
+      </c>
+      <c r="BG139" t="n">
+        <v>0.24784</v>
+      </c>
+      <c r="BH139" t="n">
+        <v>0.28256</v>
+      </c>
+      <c r="BI139" t="n">
+        <v>0.32382</v>
+      </c>
+      <c r="BJ139" t="n">
+        <v>0.30788</v>
+      </c>
+      <c r="BK139" t="n">
+        <v>0.28191</v>
+      </c>
+      <c r="BL139" t="n">
+        <v>0.00855</v>
+      </c>
+      <c r="BM139" t="n">
+        <v>0.01367</v>
+      </c>
+      <c r="BN139" t="n">
+        <v>0.27992</v>
+      </c>
+      <c r="BO139" t="n">
+        <v>0.42277</v>
+      </c>
+      <c r="BP139" t="n">
+        <v>0.3287</v>
+      </c>
+      <c r="BQ139" t="n">
+        <v>0.26694</v>
+      </c>
+      <c r="BR139" t="n">
+        <v>0.28537</v>
+      </c>
+      <c r="BS139" t="n">
+        <v>0.30821</v>
+      </c>
+      <c r="BT139" t="n">
+        <v>0.5223300000000001</v>
+      </c>
+      <c r="BU139" t="n">
+        <v>0.3216</v>
+      </c>
+      <c r="BV139" t="n">
+        <v>-0.03041</v>
+      </c>
+      <c r="BW139" t="n">
+        <v>0.41167</v>
+      </c>
+      <c r="BX139" t="n">
+        <v>0.45569</v>
+      </c>
+      <c r="BY139" t="n">
+        <v>0.50392</v>
+      </c>
+      <c r="BZ139" t="n">
+        <v>0.32249</v>
+      </c>
+      <c r="CA139" t="n">
+        <v>0.4052</v>
+      </c>
+      <c r="CB139" t="n">
+        <v>0.34969</v>
+      </c>
+      <c r="CC139" t="n">
+        <v>0.54722</v>
+      </c>
+      <c r="CD139" t="n">
+        <v>0.47761</v>
+      </c>
+      <c r="CE139" t="n">
+        <v>0.38919</v>
+      </c>
+      <c r="CF139" t="n">
+        <v>0.45522</v>
+      </c>
+      <c r="CG139" t="n">
+        <v>0.43125</v>
+      </c>
+      <c r="CH139" t="n">
+        <v>0.72936</v>
+      </c>
+      <c r="CI139" t="n">
+        <v>0.49927</v>
+      </c>
+      <c r="CJ139" t="n">
+        <v>0.42848</v>
+      </c>
+      <c r="CK139" t="n">
+        <v>0.42771</v>
+      </c>
+      <c r="CL139" t="n">
+        <v>0.40298</v>
+      </c>
+      <c r="CM139" t="n">
+        <v>0.38002</v>
+      </c>
+      <c r="CN139" t="n">
+        <v>0.39035</v>
+      </c>
+      <c r="CO139" t="n">
+        <v>0.37055</v>
+      </c>
+      <c r="CP139" t="n">
+        <v>0.38524</v>
+      </c>
+      <c r="CQ139" t="n">
+        <v>0.37274</v>
+      </c>
+      <c r="CR139" t="n">
+        <v>0.37036</v>
+      </c>
+      <c r="CS139" t="n">
+        <v>0.36903</v>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="2" t="n">
+        <v>46163</v>
+      </c>
+      <c r="B140" t="n">
+        <v>0.34705</v>
+      </c>
+      <c r="C140" t="n">
+        <v>0.46765</v>
+      </c>
+      <c r="D140" t="n">
+        <v>0.40019</v>
+      </c>
+      <c r="E140" t="n">
+        <v>0.40025</v>
+      </c>
+      <c r="F140" t="n">
+        <v>0.39053</v>
+      </c>
+      <c r="G140" t="n">
+        <v>0.3808</v>
+      </c>
+      <c r="H140" t="n">
+        <v>0.36019</v>
+      </c>
+      <c r="I140" t="n">
+        <v>0.38704</v>
+      </c>
+      <c r="J140" t="n">
+        <v>0.38992</v>
+      </c>
+      <c r="K140" t="n">
+        <v>0.37871</v>
+      </c>
+      <c r="L140" t="n">
+        <v>0.39409</v>
+      </c>
+      <c r="M140" t="n">
+        <v>0.3777799999999999</v>
+      </c>
+      <c r="N140" t="n">
+        <v>0.37452</v>
+      </c>
+      <c r="O140" t="n">
+        <v>0.37121</v>
+      </c>
+      <c r="P140" t="n">
+        <v>0.36004</v>
+      </c>
+      <c r="Q140" t="n">
+        <v>0.35987</v>
+      </c>
+      <c r="R140" t="n">
+        <v>0.36043</v>
+      </c>
+      <c r="S140" t="n">
+        <v>0.35625</v>
+      </c>
+      <c r="T140" t="n">
+        <v>0.33003</v>
+      </c>
+      <c r="U140" t="n">
+        <v>0.35622</v>
+      </c>
+      <c r="V140" t="n">
+        <v>0.35182</v>
+      </c>
+      <c r="W140" t="n">
+        <v>0.34987</v>
+      </c>
+      <c r="X140" t="n">
+        <v>0.34727</v>
+      </c>
+      <c r="Y140" t="n">
+        <v>0.35471</v>
+      </c>
+      <c r="Z140" t="n">
+        <v>0.36495</v>
+      </c>
+      <c r="AA140" t="n">
+        <v>0.37583</v>
+      </c>
+      <c r="AB140" t="n">
+        <v>0.40016</v>
+      </c>
+      <c r="AC140" t="n">
+        <v>0.38223</v>
+      </c>
+      <c r="AD140" t="n">
+        <v>0.36943</v>
+      </c>
+      <c r="AE140" t="n">
+        <v>0.35074</v>
+      </c>
+      <c r="AF140" t="n">
+        <v>0.33964</v>
+      </c>
+      <c r="AG140" t="n">
+        <v>0.2969</v>
+      </c>
+      <c r="AH140" t="n">
+        <v>0.33956</v>
+      </c>
+      <c r="AI140" t="n">
+        <v>0.30938</v>
+      </c>
+      <c r="AJ140" t="n">
+        <v>0.32309</v>
+      </c>
+      <c r="AK140" t="n">
+        <v>0.29011</v>
+      </c>
+      <c r="AL140" t="n">
+        <v>0.46186</v>
+      </c>
+      <c r="AM140" t="n">
+        <v>0.34231</v>
+      </c>
+      <c r="AN140" t="n">
+        <v>0.30703</v>
+      </c>
+      <c r="AO140" t="n">
+        <v>0.35552</v>
+      </c>
+      <c r="AP140" t="n">
+        <v>0.20894</v>
+      </c>
+      <c r="AQ140" t="n">
+        <v>0.33506</v>
+      </c>
+      <c r="AR140" t="n">
+        <v>0.17718</v>
+      </c>
+      <c r="AS140" t="n">
+        <v>0.34544</v>
+      </c>
+      <c r="AT140" t="n">
+        <v>0.23488</v>
+      </c>
+      <c r="AU140" t="n">
+        <v>0.27858</v>
+      </c>
+      <c r="AV140" t="n">
+        <v>0.28879</v>
+      </c>
+      <c r="AW140" t="n">
+        <v>0.30309</v>
+      </c>
+      <c r="AX140" t="n">
+        <v>0.27742</v>
+      </c>
+      <c r="AY140" t="n">
+        <v>0.29181</v>
+      </c>
+      <c r="AZ140" t="n">
+        <v>0.3099</v>
+      </c>
+      <c r="BA140" t="n">
+        <v>0.31362</v>
+      </c>
+      <c r="BB140" t="n">
+        <v>0.26141</v>
+      </c>
+      <c r="BC140" t="n">
+        <v>0.31939</v>
+      </c>
+      <c r="BD140" t="n">
+        <v>0.33711</v>
+      </c>
+      <c r="BE140" t="n">
+        <v>0.33448</v>
+      </c>
+      <c r="BF140" t="n">
+        <v>0.19328</v>
+      </c>
+      <c r="BG140" t="n">
+        <v>0.2953</v>
+      </c>
+      <c r="BH140" t="n">
+        <v>0.26585</v>
+      </c>
+      <c r="BI140" t="n">
+        <v>0.27647</v>
+      </c>
+      <c r="BJ140" t="n">
+        <v>0.31435</v>
+      </c>
+      <c r="BK140" t="n">
+        <v>0.31216</v>
+      </c>
+      <c r="BL140" t="n">
+        <v>0.31472</v>
+      </c>
+      <c r="BM140" t="n">
+        <v>0.30674</v>
+      </c>
+      <c r="BN140" t="n">
+        <v>0.29475</v>
+      </c>
+      <c r="BO140" t="n">
+        <v>0.36024</v>
+      </c>
+      <c r="BP140" t="n">
+        <v>0.33718</v>
+      </c>
+      <c r="BQ140" t="n">
+        <v>0.39505</v>
+      </c>
+      <c r="BR140" t="n">
+        <v>0.50019</v>
+      </c>
+      <c r="BS140" t="n">
+        <v>0.36755</v>
+      </c>
+      <c r="BT140" t="n">
+        <v>0.41465</v>
+      </c>
+      <c r="BU140" t="n">
+        <v>0.39467</v>
+      </c>
+      <c r="BV140" t="n">
+        <v>0.39176</v>
+      </c>
+      <c r="BW140" t="n">
+        <v>0.46617</v>
+      </c>
+      <c r="BX140" t="n">
+        <v>0.56036</v>
+      </c>
+      <c r="BY140" t="n">
+        <v>0.56797</v>
+      </c>
+      <c r="BZ140" t="n">
+        <v>0.38206</v>
+      </c>
+      <c r="CA140" t="n">
+        <v>0.46212</v>
+      </c>
+      <c r="CB140" t="n">
+        <v>0.55189</v>
+      </c>
+      <c r="CC140" t="n">
+        <v>0.46512</v>
+      </c>
+      <c r="CD140" t="n">
+        <v>0.37972</v>
+      </c>
+      <c r="CE140" t="n">
+        <v>0.4977</v>
+      </c>
+      <c r="CF140" t="n">
+        <v>0.39816</v>
+      </c>
+      <c r="CG140" t="n">
+        <v>0.533</v>
+      </c>
+      <c r="CH140" t="n">
+        <v>0.52074</v>
+      </c>
+      <c r="CI140" t="n">
+        <v>0.63432</v>
+      </c>
+      <c r="CJ140" t="n">
+        <v>0.68216</v>
+      </c>
+      <c r="CK140" t="n">
+        <v>0.55028</v>
+      </c>
+      <c r="CL140" t="n">
+        <v>0.5529500000000001</v>
+      </c>
+      <c r="CM140" t="n">
+        <v>0.39877</v>
+      </c>
+      <c r="CN140" t="n">
+        <v>0.44493</v>
+      </c>
+      <c r="CO140" t="n">
+        <v>0.39125</v>
+      </c>
+      <c r="CP140" t="n">
+        <v>0.37587</v>
+      </c>
+      <c r="CQ140" t="n">
+        <v>0.3805</v>
+      </c>
+      <c r="CR140" t="n">
+        <v>0.37111</v>
+      </c>
+      <c r="CS140" t="n">
+        <v>0.37686</v>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="2" t="n">
+        <v>46164</v>
+      </c>
+      <c r="B141" t="n">
+        <v>0.27247</v>
+      </c>
+      <c r="C141" t="n">
+        <v>0.36994</v>
+      </c>
+      <c r="D141" t="n">
+        <v>0.30409</v>
+      </c>
+      <c r="E141" t="n">
+        <v>0.37392</v>
+      </c>
+      <c r="F141" t="n">
+        <v>0.32986</v>
+      </c>
+      <c r="G141" t="n">
+        <v>0.33602</v>
+      </c>
+      <c r="H141" t="n">
+        <v>0.35297</v>
+      </c>
+      <c r="I141" t="n">
+        <v>0.3111</v>
+      </c>
+      <c r="J141" t="n">
+        <v>0.33187</v>
+      </c>
+      <c r="K141" t="n">
+        <v>0.34487</v>
+      </c>
+      <c r="L141" t="n">
+        <v>0.33597</v>
+      </c>
+      <c r="M141" t="n">
+        <v>0.34081</v>
+      </c>
+      <c r="N141" t="n">
+        <v>0.33139</v>
+      </c>
+      <c r="O141" t="n">
+        <v>0.33188</v>
+      </c>
+      <c r="P141" t="n">
+        <v>0.33652</v>
+      </c>
+      <c r="Q141" t="n">
+        <v>0.33057</v>
+      </c>
+      <c r="R141" t="n">
+        <v>0.30406</v>
+      </c>
+      <c r="S141" t="n">
+        <v>0.32243</v>
+      </c>
+      <c r="T141" t="n">
+        <v>0.31375</v>
+      </c>
+      <c r="U141" t="n">
+        <v>0.29783</v>
+      </c>
+      <c r="V141" t="n">
+        <v>0.2908</v>
+      </c>
+      <c r="W141" t="n">
+        <v>0.29575</v>
+      </c>
+      <c r="X141" t="n">
+        <v>0.29843</v>
+      </c>
+      <c r="Y141" t="n">
+        <v>0.27151</v>
+      </c>
+      <c r="Z141" t="n">
+        <v>0.26824</v>
+      </c>
+      <c r="AA141" t="n">
+        <v>0.33929</v>
+      </c>
+      <c r="AB141" t="n">
+        <v>0.35707</v>
+      </c>
+      <c r="AC141" t="n">
+        <v>0.27982</v>
+      </c>
+      <c r="AD141" t="n">
+        <v>0.26711</v>
+      </c>
+      <c r="AE141" t="n">
+        <v>0.26279</v>
+      </c>
+      <c r="AF141" t="n">
+        <v>0.25525</v>
+      </c>
+      <c r="AG141" t="n">
+        <v>0.2484</v>
+      </c>
+      <c r="AH141" t="n">
+        <v>0.29091</v>
+      </c>
+      <c r="AI141" t="n">
+        <v>0.23835</v>
+      </c>
+      <c r="AJ141" t="n">
+        <v>0.23703</v>
+      </c>
+      <c r="AK141" t="n">
+        <v>0.25411</v>
+      </c>
+      <c r="AL141" t="n">
+        <v>0.19016</v>
+      </c>
+      <c r="AM141" t="n">
+        <v>0.21225</v>
+      </c>
+      <c r="AN141" t="n">
+        <v>0.13438</v>
+      </c>
+      <c r="AO141" t="n">
+        <v>-0.004889999999999999</v>
+      </c>
+      <c r="AP141" t="n">
+        <v>-0.04149</v>
+      </c>
+      <c r="AQ141" t="n">
+        <v>-0.0039</v>
+      </c>
+      <c r="AR141" t="n">
+        <v>0.01264</v>
+      </c>
+      <c r="AS141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AT141" t="n">
+        <v>0.12893</v>
+      </c>
+      <c r="AU141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AV141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AW141" t="n">
+        <v>-0.05</v>
+      </c>
+      <c r="AX141" t="n">
+        <v>-0.01221</v>
+      </c>
+      <c r="AY141" t="n">
+        <v>-0.02291</v>
+      </c>
+      <c r="AZ141" t="n">
+        <v>-0.02473</v>
+      </c>
+      <c r="BA141" t="n">
+        <v>0.23542</v>
+      </c>
+      <c r="BB141" t="n">
+        <v>-0.01576</v>
+      </c>
+      <c r="BC141" t="n">
+        <v>0.02165</v>
+      </c>
+      <c r="BD141" t="n">
+        <v>0.0313</v>
+      </c>
+      <c r="BE141" t="n">
+        <v>0.02205</v>
+      </c>
+      <c r="BF141" t="n">
+        <v>0.01518</v>
+      </c>
+      <c r="BG141" t="n">
+        <v>0.01814</v>
+      </c>
+      <c r="BH141" t="n">
+        <v>0.02936</v>
+      </c>
+      <c r="BI141" t="n">
+        <v>0.10473</v>
+      </c>
+      <c r="BJ141" t="n">
+        <v>0.06423999999999999</v>
+      </c>
+      <c r="BK141" t="n">
+        <v>0.11918</v>
+      </c>
+      <c r="BL141" t="n">
+        <v>0.13787</v>
+      </c>
+      <c r="BM141" t="n">
+        <v>0.16552</v>
+      </c>
+      <c r="BN141" t="n">
+        <v>0.22316</v>
+      </c>
+      <c r="BO141" t="n">
+        <v>0.18128</v>
+      </c>
+      <c r="BP141" t="n">
+        <v>0.18602</v>
+      </c>
+      <c r="BQ141" t="n">
+        <v>0.32821</v>
+      </c>
+      <c r="BR141" t="n">
+        <v>0.29676</v>
+      </c>
+      <c r="BS141" t="n">
+        <v>0.31747</v>
+      </c>
+      <c r="BT141" t="n">
+        <v>0.3146</v>
+      </c>
+      <c r="BU141" t="n">
+        <v>0.32303</v>
+      </c>
+      <c r="BV141" t="n">
+        <v>0.20772</v>
+      </c>
+      <c r="BW141" t="n">
+        <v>0.31841</v>
+      </c>
+      <c r="BX141" t="n">
+        <v>0.333</v>
+      </c>
+      <c r="BY141" t="n">
+        <v>0.33008</v>
+      </c>
+      <c r="BZ141" t="n">
+        <v>0.25004</v>
+      </c>
+      <c r="CA141" t="n">
+        <v>0.36658</v>
+      </c>
+      <c r="CB141" t="n">
+        <v>0.38745</v>
+      </c>
+      <c r="CC141" t="n">
+        <v>0.36745</v>
+      </c>
+      <c r="CD141" t="n">
+        <v>0.3686</v>
+      </c>
+      <c r="CE141" t="n">
+        <v>0.32062</v>
+      </c>
+      <c r="CF141" t="n">
+        <v>0.39015</v>
+      </c>
+      <c r="CG141" t="n">
+        <v>0.38596</v>
+      </c>
+      <c r="CH141" t="n">
+        <v>0.37953</v>
+      </c>
+      <c r="CI141" t="n">
+        <v>0.40504</v>
+      </c>
+      <c r="CJ141" t="n">
+        <v>0.3924</v>
+      </c>
+      <c r="CK141" t="n">
+        <v>0.36403</v>
+      </c>
+      <c r="CL141" t="n">
+        <v>0.36077</v>
+      </c>
+      <c r="CM141" t="n">
+        <v>0.371</v>
+      </c>
+      <c r="CN141" t="n">
+        <v>0.41892</v>
+      </c>
+      <c r="CO141" t="n">
+        <v>0.38852</v>
+      </c>
+      <c r="CP141" t="n">
+        <v>0.38513</v>
+      </c>
+      <c r="CQ141" t="n">
+        <v>0.38472</v>
+      </c>
+      <c r="CR141" t="n">
+        <v>0.39943</v>
+      </c>
+      <c r="CS141" t="n">
+        <v>0.38076</v>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" s="2" t="n">
+        <v>46165</v>
+      </c>
+      <c r="B142" t="n">
+        <v>0.35858</v>
+      </c>
+      <c r="C142" t="n">
+        <v>0.6966</v>
+      </c>
+      <c r="D142" t="n">
+        <v>0.34049</v>
+      </c>
+      <c r="E142" t="n">
+        <v>0.36379</v>
+      </c>
+      <c r="F142" t="n">
+        <v>0.35419</v>
+      </c>
+      <c r="G142" t="n">
+        <v>0.31715</v>
+      </c>
+      <c r="H142" t="n">
+        <v>0.32908</v>
+      </c>
+      <c r="I142" t="n">
+        <v>0.32848</v>
+      </c>
+      <c r="J142" t="n">
+        <v>0.3304</v>
+      </c>
+      <c r="K142" t="n">
+        <v>0.3801</v>
+      </c>
+      <c r="L142" t="n">
+        <v>0.33407</v>
+      </c>
+      <c r="M142" t="n">
+        <v>0.33419</v>
+      </c>
+      <c r="N142" t="n">
+        <v>0.33179</v>
+      </c>
+      <c r="O142" t="n">
+        <v>0.38406</v>
+      </c>
+      <c r="P142" t="n">
+        <v>0.35022</v>
+      </c>
+      <c r="Q142" t="n">
+        <v>0.35871</v>
+      </c>
+      <c r="R142" t="n">
+        <v>0.38001</v>
+      </c>
+      <c r="S142" t="n">
+        <v>0.37326</v>
+      </c>
+      <c r="T142" t="n">
+        <v>0.33534</v>
+      </c>
+      <c r="U142" t="n">
+        <v>0.35864</v>
+      </c>
+      <c r="V142" t="n">
+        <v>0.36051</v>
+      </c>
+      <c r="W142" t="n">
+        <v>0.35874</v>
+      </c>
+      <c r="X142" t="n">
+        <v>0.36334</v>
+      </c>
+      <c r="Y142" t="n">
+        <v>0.34931</v>
+      </c>
+      <c r="Z142" t="n">
+        <v>0.3668</v>
+      </c>
+      <c r="AA142" t="n">
+        <v>0.35059</v>
+      </c>
+      <c r="AB142" t="n">
+        <v>0.35908</v>
+      </c>
+      <c r="AC142" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="AD142" t="n">
+        <v>0.30544</v>
+      </c>
+      <c r="AE142" t="n">
+        <v>0.30826</v>
+      </c>
+      <c r="AF142" t="n">
+        <v>0.29065</v>
+      </c>
+      <c r="AG142" t="n">
+        <v>0.28416</v>
+      </c>
+      <c r="AH142" t="n">
+        <v>0.27618</v>
+      </c>
+      <c r="AI142" t="n">
+        <v>0.27127</v>
+      </c>
+      <c r="AJ142" t="n">
+        <v>0.26111</v>
+      </c>
+      <c r="AK142" t="n">
+        <v>0.2327</v>
+      </c>
+      <c r="AL142" t="n">
+        <v>0.22642</v>
+      </c>
+      <c r="AM142" t="n">
+        <v>0.19549</v>
+      </c>
+      <c r="AN142" t="n">
+        <v>0.19549</v>
+      </c>
+      <c r="AO142" t="n">
+        <v>0.1999</v>
+      </c>
+      <c r="AP142" t="n">
+        <v>0.21586</v>
+      </c>
+      <c r="AQ142" t="n">
+        <v>-0.01496</v>
+      </c>
+      <c r="AR142" t="n">
+        <v>-0.01475</v>
+      </c>
+      <c r="AS142" t="n">
+        <v>-0.01693</v>
+      </c>
+      <c r="AT142" t="n">
+        <v>-0.01752</v>
+      </c>
+      <c r="AU142" t="n">
+        <v>0.03613</v>
+      </c>
+      <c r="AV142" t="n">
+        <v>0.07811</v>
+      </c>
+      <c r="AW142" t="n">
+        <v>-0.03603</v>
+      </c>
+      <c r="AX142" t="n">
+        <v>-0.00457</v>
+      </c>
+      <c r="AY142" t="n">
+        <v>0.0139</v>
+      </c>
+      <c r="AZ142" t="n">
+        <v>0.0443</v>
+      </c>
+      <c r="BA142" t="n">
+        <v>-0.00801</v>
+      </c>
+      <c r="BB142" t="n">
+        <v>-0.008369999999999999</v>
+      </c>
+      <c r="BC142" t="n">
+        <v>-0.00182</v>
+      </c>
+      <c r="BD142" t="n">
+        <v>0.15544</v>
+      </c>
+      <c r="BE142" t="n">
+        <v>-0.0449</v>
+      </c>
+      <c r="BF142" t="n">
+        <v>-0.01552</v>
+      </c>
+      <c r="BG142" t="n">
+        <v>-0.01185</v>
+      </c>
+      <c r="BH142" t="n">
+        <v>-0.008840000000000001</v>
+      </c>
+      <c r="BI142" t="n">
+        <v>0.00464</v>
+      </c>
+      <c r="BJ142" t="n">
+        <v>-0.01514</v>
+      </c>
+      <c r="BK142" t="n">
+        <v>-0.01864</v>
+      </c>
+      <c r="BL142" t="n">
+        <v>-0.02116</v>
+      </c>
+      <c r="BM142" t="n">
+        <v>0.05855</v>
+      </c>
+      <c r="BN142" t="n">
+        <v>0.22558</v>
+      </c>
+      <c r="BO142" t="n">
+        <v>0.1824</v>
+      </c>
+      <c r="BP142" t="n">
+        <v>0.23438</v>
+      </c>
+      <c r="BQ142" t="n">
+        <v>0.29357</v>
+      </c>
+      <c r="BR142" t="n">
+        <v>0.26862</v>
+      </c>
+      <c r="BS142" t="n">
+        <v>0.43007</v>
+      </c>
+      <c r="BT142" t="n">
+        <v>0.38292</v>
+      </c>
+      <c r="BU142" t="n">
+        <v>0.39331</v>
+      </c>
+      <c r="BV142" t="n">
+        <v>0.3618</v>
+      </c>
+      <c r="BW142" t="n">
+        <v>0.38231</v>
+      </c>
+      <c r="BX142" t="n">
+        <v>0.40012</v>
+      </c>
+      <c r="BY142" t="n">
+        <v>0.35659</v>
+      </c>
+      <c r="BZ142" t="n">
+        <v>0.34989</v>
+      </c>
+      <c r="CA142" t="n">
+        <v>0.38694</v>
+      </c>
+      <c r="CB142" t="n">
+        <v>0.52811</v>
+      </c>
+      <c r="CC142" t="n">
+        <v>0.41455</v>
+      </c>
+      <c r="CD142" t="n">
+        <v>0.38944</v>
+      </c>
+      <c r="CE142" t="n">
+        <v>0.38506</v>
+      </c>
+      <c r="CF142" t="n">
+        <v>0.39774</v>
+      </c>
+      <c r="CG142" t="n">
+        <v>0.38527</v>
+      </c>
+      <c r="CH142" t="n">
+        <v>0.38667</v>
+      </c>
+      <c r="CI142" t="n">
+        <v>0.40857</v>
+      </c>
+      <c r="CJ142" t="n">
+        <v>0.36096</v>
+      </c>
+      <c r="CK142" t="n">
+        <v>0.38922</v>
+      </c>
+      <c r="CL142" t="n">
+        <v>0.43152</v>
+      </c>
+      <c r="CM142" t="n">
+        <v>0.39233</v>
+      </c>
+      <c r="CN142" t="n">
+        <v>0.37515</v>
+      </c>
+      <c r="CO142" t="n">
+        <v>0.38599</v>
+      </c>
+      <c r="CP142" t="n">
+        <v>0.37081</v>
+      </c>
+      <c r="CQ142" t="n">
+        <v>0.35923</v>
+      </c>
+      <c r="CR142" t="n">
+        <v>0.35646</v>
+      </c>
+      <c r="CS142" t="n">
+        <v>0.37207</v>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" s="2" t="n">
+        <v>46166</v>
+      </c>
+      <c r="B143" t="n">
+        <v>0.32375</v>
+      </c>
+      <c r="C143" t="n">
+        <v>0.51223</v>
+      </c>
+      <c r="D143" t="n">
+        <v>0.39193</v>
+      </c>
+      <c r="E143" t="n">
+        <v>0.39572</v>
+      </c>
+      <c r="F143" t="n">
+        <v>0.29957</v>
+      </c>
+      <c r="G143" t="n">
+        <v>0.36615</v>
+      </c>
+      <c r="H143" t="n">
+        <v>0.35369</v>
+      </c>
+      <c r="I143" t="n">
+        <v>0.36282</v>
+      </c>
+      <c r="J143" t="n">
+        <v>0.33675</v>
+      </c>
+      <c r="K143" t="n">
+        <v>0.41723</v>
+      </c>
+      <c r="L143" t="n">
+        <v>0.33557</v>
+      </c>
+      <c r="M143" t="n">
+        <v>0.37102</v>
+      </c>
+      <c r="N143" t="n">
+        <v>0.3704</v>
+      </c>
+      <c r="O143" t="n">
+        <v>0.33332</v>
+      </c>
+      <c r="P143" t="n">
+        <v>0.33156</v>
+      </c>
+      <c r="Q143" t="n">
+        <v>0.3434700000000001</v>
+      </c>
+      <c r="R143" t="n">
+        <v>0.32812</v>
+      </c>
+      <c r="S143" t="n">
+        <v>0.30064</v>
+      </c>
+      <c r="T143" t="n">
+        <v>0.34531</v>
+      </c>
+      <c r="U143" t="n">
+        <v>0.31111</v>
+      </c>
+      <c r="V143" t="n">
+        <v>0.30717</v>
+      </c>
+      <c r="W143" t="n">
+        <v>0.32384</v>
+      </c>
+      <c r="X143" t="n">
+        <v>0.36461</v>
+      </c>
+      <c r="Y143" t="n">
+        <v>0.33292</v>
+      </c>
+      <c r="Z143" t="n">
+        <v>0.34957</v>
+      </c>
+      <c r="AA143" t="n">
+        <v>0.33392</v>
+      </c>
+      <c r="AB143" t="n">
+        <v>0.35</v>
+      </c>
+      <c r="AC143" t="n">
+        <v>0.3326</v>
+      </c>
+      <c r="AD143" t="n">
+        <v>0.3109</v>
+      </c>
+      <c r="AE143" t="n">
+        <v>0.27163</v>
+      </c>
+      <c r="AF143" t="n">
+        <v>0.23179</v>
+      </c>
+      <c r="AG143" t="n">
+        <v>0.18653</v>
+      </c>
+      <c r="AH143" t="n">
+        <v>0.17172</v>
+      </c>
+      <c r="AI143" t="n">
+        <v>0.11254</v>
+      </c>
+      <c r="AJ143" t="n">
+        <v>0.14783</v>
+      </c>
+      <c r="AK143" t="n">
+        <v>0.17421</v>
+      </c>
+      <c r="AL143" t="n">
+        <v>0.16158</v>
+      </c>
+      <c r="AM143" t="n">
+        <v>0.08704000000000001</v>
+      </c>
+      <c r="AN143" t="n">
+        <v>0.10407</v>
+      </c>
+      <c r="AO143" t="n">
+        <v>0.04751</v>
+      </c>
+      <c r="AP143" t="n">
+        <v>0.06979</v>
+      </c>
+      <c r="AQ143" t="n">
+        <v>0.03641</v>
+      </c>
+      <c r="AR143" t="n">
+        <v>0.03721</v>
+      </c>
+      <c r="AS143" t="n">
+        <v>0.03787</v>
+      </c>
+      <c r="AT143" t="n">
+        <v>0.03665</v>
+      </c>
+      <c r="AU143" t="n">
+        <v>0.04527</v>
+      </c>
+      <c r="AV143" t="n">
+        <v>0.05146</v>
+      </c>
+      <c r="AW143" t="n">
+        <v>0.05968</v>
+      </c>
+      <c r="AX143" t="n">
+        <v>0.0346</v>
+      </c>
+      <c r="AY143" t="n">
+        <v>0.05656</v>
+      </c>
+      <c r="AZ143" t="n">
+        <v>0.07158</v>
+      </c>
+      <c r="BA143" t="n">
+        <v>0.11418</v>
+      </c>
+      <c r="BB143" t="n">
+        <v>0.1416</v>
+      </c>
+      <c r="BC143" t="n">
+        <v>0.08618000000000001</v>
+      </c>
+      <c r="BD143" t="n">
+        <v>0.16276</v>
+      </c>
+      <c r="BE143" t="n">
+        <v>0.14421</v>
+      </c>
+      <c r="BF143" t="n">
+        <v>0.08898</v>
+      </c>
+      <c r="BG143" t="n">
+        <v>0.04608</v>
+      </c>
+      <c r="BH143" t="n">
+        <v>0.21436</v>
+      </c>
+      <c r="BI143" t="n">
+        <v>0.09531999999999999</v>
+      </c>
+      <c r="BJ143" t="n">
+        <v>0.09090999999999999</v>
+      </c>
+      <c r="BK143" t="n">
+        <v>0.18672</v>
+      </c>
+      <c r="BL143" t="n">
+        <v>0.12973</v>
+      </c>
+      <c r="BM143" t="n">
+        <v>0.14037</v>
+      </c>
+      <c r="BN143" t="n">
+        <v>0.16605</v>
+      </c>
+      <c r="BO143" t="n">
+        <v>0.14591</v>
+      </c>
+      <c r="BP143" t="n">
+        <v>0.18061</v>
+      </c>
+      <c r="BQ143" t="n">
+        <v>0.19955</v>
+      </c>
+      <c r="BR143" t="n">
+        <v>0.20059</v>
+      </c>
+      <c r="BS143" t="n">
+        <v>0.21337</v>
+      </c>
+      <c r="BT143" t="n">
+        <v>0.25481</v>
+      </c>
+      <c r="BU143" t="n">
+        <v>0.25873</v>
+      </c>
+      <c r="BV143" t="n">
+        <v>0.26027</v>
+      </c>
+      <c r="BW143" t="n">
+        <v>0.28227</v>
+      </c>
+      <c r="BX143" t="n">
+        <v>0.36259</v>
+      </c>
+      <c r="BY143" t="n">
+        <v>0.4040899999999999</v>
+      </c>
+      <c r="BZ143" t="n">
+        <v>0.33495</v>
+      </c>
+      <c r="CA143" t="n">
+        <v>0.31901</v>
+      </c>
+      <c r="CB143" t="n">
+        <v>0.27299</v>
+      </c>
+      <c r="CC143" t="n">
+        <v>0.33665</v>
+      </c>
+      <c r="CD143" t="n">
+        <v>0.38778</v>
+      </c>
+      <c r="CE143" t="n">
+        <v>0.3771600000000001</v>
+      </c>
+      <c r="CF143" t="n">
+        <v>0.37717</v>
+      </c>
+      <c r="CG143" t="n">
+        <v>0.3553</v>
+      </c>
+      <c r="CH143" t="n">
+        <v>0.38529</v>
+      </c>
+      <c r="CI143" t="n">
+        <v>0.4134</v>
+      </c>
+      <c r="CJ143" t="n">
+        <v>0.42009</v>
+      </c>
+      <c r="CK143" t="n">
+        <v>0.49778</v>
+      </c>
+      <c r="CL143" t="n">
+        <v>0.41</v>
+      </c>
+      <c r="CM143" t="n">
+        <v>0.41832</v>
+      </c>
+      <c r="CN143" t="n">
+        <v>0.44327</v>
+      </c>
+      <c r="CO143" t="n">
+        <v>0.41524</v>
+      </c>
+      <c r="CP143" t="n">
+        <v>0.39747</v>
+      </c>
+      <c r="CQ143" t="n">
+        <v>0.4156</v>
+      </c>
+      <c r="CR143" t="n">
+        <v>0.41473</v>
+      </c>
+      <c r="CS143" t="n">
+        <v>0.38217</v>
       </c>
     </row>
   </sheetData>
